--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -14020,7 +14020,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -14028,34 +14028,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H201" s="5" t="n">
+        <v>7762000</v>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>24106</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L201" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>6908180</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>21454</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
@@ -14090,7 +14082,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14098,34 +14090,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I202" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H202" s="5" t="n">
+        <v>5875000</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>23594</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K202" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L202" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>5228750</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>20999</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N202" s="3" t="inlineStr">
@@ -14160,7 +14144,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -14168,34 +14152,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I203" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H203" s="5" t="n">
+        <v>7589000</v>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>23790</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K203" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L203" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>6754210</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>21173</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N203" s="3" t="inlineStr">
@@ -14230,7 +14206,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -14238,34 +14214,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H204" s="5" t="n">
+        <v>7551000</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>23671</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L204" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>6720390</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>21067</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
@@ -14300,7 +14268,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -14308,34 +14276,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H205" s="5" t="n">
+        <v>7361000</v>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>23669</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L205" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>6551290</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>21065</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -14370,7 +14330,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14378,34 +14338,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H206" s="5" t="n">
+        <v>7757000</v>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>23506</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L206" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>6903730</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>20920</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
@@ -14650,7 +14602,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -14658,34 +14610,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H210" s="5" t="n">
+        <v>7743000</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>24047</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L210" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>6891270</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>21401</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -14720,7 +14664,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14728,34 +14672,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H211" s="5" t="n">
+        <v>5860000</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>23534</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L211" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>5215400</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>20945</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
@@ -14790,7 +14726,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -14798,34 +14734,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H212" s="5" t="n">
+        <v>7570000</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>23730</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L212" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>6737300</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>21120</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">
@@ -14860,7 +14788,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14868,34 +14796,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H213" s="5" t="n">
+        <v>7532000</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>23611</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L213" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>6703480</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>21014</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -14930,7 +14850,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -14938,34 +14858,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H214" s="5" t="n">
+        <v>7343000</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>23611</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L214" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>6535270</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>21014</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -15000,7 +14912,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -15008,34 +14920,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>7737000</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>23445</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L215" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>6885930</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>20866</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -15350,7 +15254,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15358,34 +15262,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H220" s="5" t="n">
+        <v>7704000</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>23925</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L220" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>6856560</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>21294</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
@@ -15420,7 +15316,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15428,34 +15324,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>5831000</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>23418</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L221" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>5189590</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>20842</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15490,7 +15378,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -15498,34 +15386,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H222" s="5" t="n">
+        <v>7532000</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>23611</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L222" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>6703480</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>21014</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
@@ -15560,7 +15440,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -15568,34 +15448,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H223" s="5" t="n">
+        <v>7495000</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>23495</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L223" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>6670550</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>20911</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -15630,7 +15502,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -15638,34 +15510,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>7307000</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>23495</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L224" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>6503230</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>20911</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -15700,7 +15564,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -15708,34 +15572,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H225" s="5" t="n">
+        <v>7699000</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>23330</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L225" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>6852110</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>20764</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -16050,7 +15906,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -16058,34 +15914,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H230" s="5" t="n">
+        <v>7685000</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>23866</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L230" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>6839650</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>21241</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
@@ -16306,7 +16154,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -16314,34 +16162,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H234" s="5" t="n">
+        <v>7288000</v>
+      </c>
+      <c r="I234" s="5" t="n">
+        <v>23434</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L234" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>6486320</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>20856</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
@@ -16710,7 +16550,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -16718,34 +16558,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H240" s="5" t="n">
+        <v>7666000</v>
+      </c>
+      <c r="I240" s="5" t="n">
+        <v>23807</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L240" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>6822740</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>21189</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -16966,7 +16798,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -16974,34 +16806,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H244" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I244" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H244" s="5" t="n">
+        <v>7270000</v>
+      </c>
+      <c r="I244" s="5" t="n">
+        <v>23376</v>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K244" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L244" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>6470300</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>20805</v>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
@@ -17370,7 +17194,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -17378,34 +17202,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H250" s="5" t="n">
+        <v>7647000</v>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>23748</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L250" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>6805830</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>21136</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -17626,7 +17442,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -17634,34 +17450,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H254" s="5" t="n">
+        <v>7252000</v>
+      </c>
+      <c r="I254" s="5" t="n">
+        <v>23318</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L254" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>6454280</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>20753</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
@@ -18030,7 +17838,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -18038,34 +17846,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H260" s="5" t="n">
+        <v>7628000</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>23689</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L260" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>6788920</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>21084</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
@@ -18286,7 +18086,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -18294,34 +18094,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H264" s="5" t="n">
+        <v>7234000</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>23260</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L264" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>6438260</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>20702</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
@@ -18690,7 +18482,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -18698,34 +18490,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H270" s="5" t="n">
+        <v>7609000</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>23630</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>6772010</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>21031</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
@@ -18946,7 +18730,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -18954,34 +18738,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H274" s="5" t="n">
+        <v>7216000</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>23203</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L274" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>6422240</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>20650</v>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
@@ -19350,7 +19126,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -19358,34 +19134,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H280" s="5" t="n">
+        <v>7590000</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>23571</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L280" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>6755100</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>20979</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
@@ -19606,7 +19374,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -19614,34 +19382,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H284" s="5" t="n">
+        <v>7198000</v>
+      </c>
+      <c r="I284" s="5" t="n">
+        <v>23145</v>
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L284" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>6406220</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>20599</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
@@ -20010,7 +19770,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -20018,34 +19778,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H290" s="5" t="n">
+        <v>7571000</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>23512</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L290" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>6738190</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>20926</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N290" s="3" t="inlineStr">
@@ -20266,7 +20018,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -20274,34 +20026,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H294" s="5" t="n">
+        <v>7180000</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>23087</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L294" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>6390200</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>20547</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -20670,7 +20414,7 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -20678,34 +20422,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H300" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I300" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H300" s="5" t="n">
+        <v>7552000</v>
+      </c>
+      <c r="I300" s="5" t="n">
+        <v>23453</v>
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K300" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L300" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K300" s="5" t="n">
+        <v>6721280</v>
+      </c>
+      <c r="L300" s="5" t="n">
+        <v>20874</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N300" s="3" t="inlineStr">
@@ -20740,7 +20476,7 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -20748,34 +20484,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H301" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I301" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H301" s="5" t="n">
+        <v>5715000</v>
+      </c>
+      <c r="I301" s="5" t="n">
+        <v>22952</v>
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K301" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L301" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K301" s="5" t="n">
+        <v>5086350</v>
+      </c>
+      <c r="L301" s="5" t="n">
+        <v>20427</v>
       </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N301" s="3" t="inlineStr">
@@ -20810,7 +20538,7 @@
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -20818,34 +20546,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I302" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H302" s="5" t="n">
+        <v>7383000</v>
+      </c>
+      <c r="I302" s="5" t="n">
+        <v>23144</v>
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K302" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L302" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K302" s="5" t="n">
+        <v>6570870</v>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>20598</v>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N302" s="3" t="inlineStr">
@@ -20880,7 +20600,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -20888,34 +20608,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H303" s="5" t="n">
+        <v>7346000</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>23028</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="n">
+        <v>6537940</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>20495</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N303" s="3" t="inlineStr">
@@ -20950,7 +20662,7 @@
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -20958,34 +20670,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H304" s="5" t="n">
+        <v>7162000</v>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>23029</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L304" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K304" s="5" t="n">
+        <v>6374180</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>20496</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N304" s="3" t="inlineStr">
@@ -21020,7 +20724,7 @@
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -21028,34 +20732,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H305" s="5" t="n">
+        <v>7546000</v>
+      </c>
+      <c r="I305" s="5" t="n">
+        <v>22867</v>
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L305" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K305" s="5" t="n">
+        <v>6715940</v>
+      </c>
+      <c r="L305" s="5" t="n">
+        <v>20351</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -21362,7 +21058,7 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -21370,34 +21066,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H310" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I310" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H310" s="5" t="n">
+        <v>7514000</v>
+      </c>
+      <c r="I310" s="5" t="n">
+        <v>23335</v>
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K310" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L310" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K310" s="5" t="n">
+        <v>6687460</v>
+      </c>
+      <c r="L310" s="5" t="n">
+        <v>20769</v>
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N310" s="3" t="inlineStr">
@@ -21618,7 +21306,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -21626,34 +21314,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H314" s="5" t="n">
+        <v>7126000</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>22913</v>
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="n">
+        <v>6342140</v>
+      </c>
+      <c r="L314" s="5" t="n">
+        <v>20393</v>
       </c>
       <c r="M314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N314" s="3" t="inlineStr">
@@ -22014,7 +21694,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -22022,34 +21702,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H320" s="5" t="n">
+        <v>7496000</v>
+      </c>
+      <c r="I320" s="5" t="n">
+        <v>23280</v>
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L320" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K320" s="5" t="n">
+        <v>6671440</v>
+      </c>
+      <c r="L320" s="5" t="n">
+        <v>20719</v>
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N320" s="3" t="inlineStr">
@@ -22270,7 +21942,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -22278,34 +21950,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H324" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I324" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H324" s="5" t="n">
+        <v>7109000</v>
+      </c>
+      <c r="I324" s="5" t="n">
+        <v>22859</v>
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K324" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L324" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K324" s="5" t="n">
+        <v>6327010</v>
+      </c>
+      <c r="L324" s="5" t="n">
+        <v>20344</v>
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N324" s="3" t="inlineStr">
@@ -22666,7 +22330,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -22674,34 +22338,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H330" s="5" t="n">
+        <v>7477000</v>
+      </c>
+      <c r="I330" s="5" t="n">
+        <v>23220</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L330" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K330" s="5" t="n">
+        <v>6654530</v>
+      </c>
+      <c r="L330" s="5" t="n">
+        <v>20666</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -22922,7 +22578,7 @@
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -22930,34 +22586,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H334" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I334" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H334" s="5" t="n">
+        <v>7091000</v>
+      </c>
+      <c r="I334" s="5" t="n">
+        <v>22801</v>
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K334" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L334" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K334" s="5" t="n">
+        <v>6310990</v>
+      </c>
+      <c r="L334" s="5" t="n">
+        <v>20293</v>
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N334" s="3" t="inlineStr">
@@ -23318,7 +22966,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -23326,34 +22974,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H340" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I340" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H340" s="5" t="n">
+        <v>7458000</v>
+      </c>
+      <c r="I340" s="5" t="n">
+        <v>23161</v>
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K340" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L340" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K340" s="5" t="n">
+        <v>6637620</v>
+      </c>
+      <c r="L340" s="5" t="n">
+        <v>20614</v>
       </c>
       <c r="M340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N340" s="3" t="inlineStr">
@@ -23574,7 +23214,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -23582,34 +23222,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H344" s="5" t="n">
+        <v>7073000</v>
+      </c>
+      <c r="I344" s="5" t="n">
+        <v>22743</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L344" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K344" s="5" t="n">
+        <v>6294970</v>
+      </c>
+      <c r="L344" s="5" t="n">
+        <v>20241</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N344" s="3" t="inlineStr">
@@ -23970,7 +23602,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -23978,34 +23610,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H350" s="5" t="n">
+        <v>7440000</v>
+      </c>
+      <c r="I350" s="5" t="n">
+        <v>23106</v>
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K350" s="5" t="n">
+        <v>6621600</v>
+      </c>
+      <c r="L350" s="5" t="n">
+        <v>20564</v>
       </c>
       <c r="M350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N350" s="3" t="inlineStr">
@@ -24226,7 +23850,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -24234,34 +23858,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H354" s="5" t="n">
+        <v>7056000</v>
+      </c>
+      <c r="I354" s="5" t="n">
+        <v>22688</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L354" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K354" s="5" t="n">
+        <v>6279840</v>
+      </c>
+      <c r="L354" s="5" t="n">
+        <v>20192</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N354" s="3" t="inlineStr">
@@ -24622,7 +24238,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -24630,34 +24246,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H360" s="5" t="n">
+        <v>7421000</v>
+      </c>
+      <c r="I360" s="5" t="n">
+        <v>23047</v>
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L360" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K360" s="5" t="n">
+        <v>6604690</v>
+      </c>
+      <c r="L360" s="5" t="n">
+        <v>20511</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -24878,7 +24486,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -24886,34 +24494,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H364" s="5" t="n">
+        <v>7038000</v>
+      </c>
+      <c r="I364" s="5" t="n">
+        <v>22630</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L364" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K364" s="5" t="n">
+        <v>6263820</v>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>20141</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N364" s="3" t="inlineStr">
@@ -25274,7 +24874,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -25282,34 +24882,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H370" s="5" t="n">
+        <v>7403000</v>
+      </c>
+      <c r="I370" s="5" t="n">
+        <v>22991</v>
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L370" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K370" s="5" t="n">
+        <v>6588670</v>
+      </c>
+      <c r="L370" s="5" t="n">
+        <v>20462</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N370" s="3" t="inlineStr">
@@ -25530,7 +25122,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -25538,34 +25130,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H374" s="5" t="n">
+        <v>7021000</v>
+      </c>
+      <c r="I374" s="5" t="n">
+        <v>22576</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L374" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K374" s="5" t="n">
+        <v>6248690</v>
+      </c>
+      <c r="L374" s="5" t="n">
+        <v>20092</v>
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N374" s="3" t="inlineStr">
@@ -25926,7 +25510,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -25934,34 +25518,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H380" s="5" t="n">
+        <v>7384000</v>
+      </c>
+      <c r="I380" s="5" t="n">
+        <v>22932</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L380" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K380" s="5" t="n">
+        <v>6571760</v>
+      </c>
+      <c r="L380" s="5" t="n">
+        <v>20409</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N380" s="3" t="inlineStr">
@@ -26182,7 +25758,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -26190,34 +25766,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H384" s="5" t="n">
+        <v>7003000</v>
+      </c>
+      <c r="I384" s="5" t="n">
+        <v>22518</v>
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L384" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K384" s="5" t="n">
+        <v>6232670</v>
+      </c>
+      <c r="L384" s="5" t="n">
+        <v>20041</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -26578,7 +26146,7 @@
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
@@ -26586,34 +26154,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H390" s="5" t="n">
+        <v>7366000</v>
+      </c>
+      <c r="I390" s="5" t="n">
+        <v>22876</v>
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L390" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K390" s="5" t="n">
+        <v>6555740</v>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>20359</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -26834,7 +26394,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -26842,34 +26402,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H394" s="5" t="n">
+        <v>6986000</v>
+      </c>
+      <c r="I394" s="5" t="n">
+        <v>22463</v>
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K394" s="5" t="n">
+        <v>6217540</v>
+      </c>
+      <c r="L394" s="5" t="n">
+        <v>19992</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -27230,7 +26782,7 @@
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -27238,34 +26790,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H400" s="5" t="n">
+        <v>7329000</v>
+      </c>
+      <c r="I400" s="5" t="n">
+        <v>22761</v>
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L400" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K400" s="5" t="n">
+        <v>6522810</v>
+      </c>
+      <c r="L400" s="5" t="n">
+        <v>20257</v>
       </c>
       <c r="M400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N400" s="3" t="inlineStr">
@@ -27486,7 +27030,7 @@
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -27494,34 +27038,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H404" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I404" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H404" s="5" t="n">
+        <v>6951000</v>
+      </c>
+      <c r="I404" s="5" t="n">
+        <v>22350</v>
       </c>
       <c r="J404" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K404" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L404" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K404" s="5" t="n">
+        <v>6186390</v>
+      </c>
+      <c r="L404" s="5" t="n">
+        <v>19892</v>
       </c>
       <c r="M404" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N404" s="3" t="inlineStr">
@@ -27882,7 +27418,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -27890,34 +27426,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H410" s="5" t="n">
+        <v>7311000</v>
+      </c>
+      <c r="I410" s="5" t="n">
+        <v>22705</v>
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L410" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K410" s="5" t="n">
+        <v>6506790</v>
+      </c>
+      <c r="L410" s="5" t="n">
+        <v>20207</v>
       </c>
       <c r="M410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N410" s="3" t="inlineStr">
@@ -28138,7 +27666,7 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -28146,34 +27674,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H414" s="5" t="n">
+        <v>6933000</v>
+      </c>
+      <c r="I414" s="5" t="n">
+        <v>22293</v>
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L414" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K414" s="5" t="n">
+        <v>6170370</v>
+      </c>
+      <c r="L414" s="5" t="n">
+        <v>19840</v>
       </c>
       <c r="M414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N414" s="3" t="inlineStr">
@@ -28534,7 +28054,7 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -28542,34 +28062,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H420" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I420" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H420" s="5" t="n">
+        <v>7293000</v>
+      </c>
+      <c r="I420" s="5" t="n">
+        <v>22649</v>
       </c>
       <c r="J420" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K420" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L420" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K420" s="5" t="n">
+        <v>6490770</v>
+      </c>
+      <c r="L420" s="5" t="n">
+        <v>20158</v>
       </c>
       <c r="M420" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N420" s="3" t="inlineStr">
@@ -28790,7 +28302,7 @@
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
@@ -28798,34 +28310,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H424" s="5" t="n">
+        <v>6916000</v>
+      </c>
+      <c r="I424" s="5" t="n">
+        <v>22238</v>
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L424" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K424" s="5" t="n">
+        <v>6155240</v>
+      </c>
+      <c r="L424" s="5" t="n">
+        <v>19792</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N424" s="3" t="inlineStr">
@@ -29186,7 +28690,7 @@
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
@@ -29194,34 +28698,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H430" s="5" t="n">
+        <v>7275000</v>
+      </c>
+      <c r="I430" s="5" t="n">
+        <v>22593</v>
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L430" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K430" s="5" t="n">
+        <v>6474750</v>
+      </c>
+      <c r="L430" s="5" t="n">
+        <v>20108</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -29442,7 +28938,7 @@
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -29450,34 +28946,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H434" s="5" t="n">
+        <v>6899000</v>
+      </c>
+      <c r="I434" s="5" t="n">
+        <v>22183</v>
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L434" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K434" s="5" t="n">
+        <v>6140110</v>
+      </c>
+      <c r="L434" s="5" t="n">
+        <v>19743</v>
       </c>
       <c r="M434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N434" s="3" t="inlineStr">
@@ -29838,7 +29326,7 @@
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
@@ -29846,34 +29334,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H440" s="5" t="n">
+        <v>7256000</v>
+      </c>
+      <c r="I440" s="5" t="n">
+        <v>22534</v>
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L440" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K440" s="5" t="n">
+        <v>6457840</v>
+      </c>
+      <c r="L440" s="5" t="n">
+        <v>20055</v>
       </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N440" s="3" t="inlineStr">
@@ -30094,7 +29574,7 @@
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
@@ -30102,34 +29582,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H444" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I444" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H444" s="5" t="n">
+        <v>6882000</v>
+      </c>
+      <c r="I444" s="5" t="n">
+        <v>22129</v>
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K444" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L444" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K444" s="5" t="n">
+        <v>6124980</v>
+      </c>
+      <c r="L444" s="5" t="n">
+        <v>19694</v>
       </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N444" s="3" t="inlineStr">
@@ -30490,7 +29962,7 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr">
@@ -30498,34 +29970,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H450" s="5" t="n">
+        <v>7238000</v>
+      </c>
+      <c r="I450" s="5" t="n">
+        <v>22478</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L450" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K450" s="5" t="n">
+        <v>6441820</v>
+      </c>
+      <c r="L450" s="5" t="n">
+        <v>20006</v>
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N450" s="3" t="inlineStr">
@@ -30746,7 +30210,7 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
@@ -30754,34 +30218,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H454" s="5" t="n">
+        <v>6865000</v>
+      </c>
+      <c r="I454" s="5" t="n">
+        <v>22074</v>
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L454" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K454" s="5" t="n">
+        <v>6109850</v>
+      </c>
+      <c r="L454" s="5" t="n">
+        <v>19646</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -31142,7 +30598,7 @@
       </c>
       <c r="F460" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G460" s="3" t="inlineStr">
@@ -31150,34 +30606,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H460" s="5" t="n">
+        <v>7220000</v>
+      </c>
+      <c r="I460" s="5" t="n">
+        <v>22422</v>
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L460" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K460" s="5" t="n">
+        <v>6425800</v>
+      </c>
+      <c r="L460" s="5" t="n">
+        <v>19956</v>
       </c>
       <c r="M460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N460" s="3" t="inlineStr">
@@ -31398,7 +30846,7 @@
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
@@ -31406,34 +30854,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H464" s="5" t="n">
+        <v>6847000</v>
+      </c>
+      <c r="I464" s="5" t="n">
+        <v>22016</v>
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L464" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K464" s="5" t="n">
+        <v>6093830</v>
+      </c>
+      <c r="L464" s="5" t="n">
+        <v>19594</v>
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N464" s="3" t="inlineStr">
@@ -31794,7 +31234,7 @@
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -31802,34 +31242,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H470" s="5" t="n">
+        <v>7202000</v>
+      </c>
+      <c r="I470" s="5" t="n">
+        <v>22366</v>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L470" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K470" s="5" t="n">
+        <v>6409780</v>
+      </c>
+      <c r="L470" s="5" t="n">
+        <v>19906</v>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N470" s="3" t="inlineStr">
@@ -32050,7 +31482,7 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -32058,34 +31490,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H474" s="5" t="n">
+        <v>6830000</v>
+      </c>
+      <c r="I474" s="5" t="n">
+        <v>21961</v>
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L474" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K474" s="5" t="n">
+        <v>6078700</v>
+      </c>
+      <c r="L474" s="5" t="n">
+        <v>19546</v>
       </c>
       <c r="M474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N474" s="3" t="inlineStr">
@@ -32446,7 +31870,7 @@
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
@@ -32454,34 +31878,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H480" s="5" t="n">
+        <v>7166000</v>
+      </c>
+      <c r="I480" s="5" t="n">
+        <v>22255</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L480" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K480" s="5" t="n">
+        <v>6377740</v>
+      </c>
+      <c r="L480" s="5" t="n">
+        <v>19807</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N480" s="3" t="inlineStr">
@@ -32702,7 +32118,7 @@
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
@@ -32710,34 +32126,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H484" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I484" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H484" s="5" t="n">
+        <v>6796000</v>
+      </c>
+      <c r="I484" s="5" t="n">
+        <v>21852</v>
       </c>
       <c r="J484" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K484" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L484" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K484" s="5" t="n">
+        <v>6048440</v>
+      </c>
+      <c r="L484" s="5" t="n">
+        <v>19448</v>
       </c>
       <c r="M484" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N484" s="3" t="inlineStr">
@@ -33098,7 +32506,7 @@
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr">
@@ -33106,34 +32514,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H490" s="5" t="n">
+        <v>7149000</v>
+      </c>
+      <c r="I490" s="5" t="n">
+        <v>22202</v>
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L490" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K490" s="5" t="n">
+        <v>6362610</v>
+      </c>
+      <c r="L490" s="5" t="n">
+        <v>19760</v>
       </c>
       <c r="M490" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N490" s="3" t="inlineStr">
@@ -33354,7 +32754,7 @@
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
@@ -33362,34 +32762,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H494" s="5" t="n">
+        <v>6779000</v>
+      </c>
+      <c r="I494" s="5" t="n">
+        <v>21797</v>
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L494" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K494" s="5" t="n">
+        <v>6033310</v>
+      </c>
+      <c r="L494" s="5" t="n">
+        <v>19400</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N494" s="3" t="inlineStr">
@@ -33758,7 +33150,7 @@
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
@@ -33766,34 +33158,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H500" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I500" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H500" s="5" t="n">
+        <v>7131000</v>
+      </c>
+      <c r="I500" s="5" t="n">
+        <v>22146</v>
       </c>
       <c r="J500" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K500" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L500" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K500" s="5" t="n">
+        <v>6346590</v>
+      </c>
+      <c r="L500" s="5" t="n">
+        <v>19710</v>
       </c>
       <c r="M500" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N500" s="3" t="inlineStr">
@@ -33828,7 +33212,7 @@
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr">
@@ -33836,34 +33220,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H501" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I501" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H501" s="5" t="n">
+        <v>5397000</v>
+      </c>
+      <c r="I501" s="5" t="n">
+        <v>21675</v>
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K501" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L501" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K501" s="5" t="n">
+        <v>4803330</v>
+      </c>
+      <c r="L501" s="5" t="n">
+        <v>19290</v>
       </c>
       <c r="M501" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N501" s="3" t="inlineStr">
@@ -33898,7 +33274,7 @@
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
@@ -33906,34 +33282,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H502" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I502" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H502" s="5" t="n">
+        <v>6936000</v>
+      </c>
+      <c r="I502" s="5" t="n">
+        <v>21743</v>
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K502" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L502" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K502" s="5" t="n">
+        <v>6173040</v>
+      </c>
+      <c r="L502" s="5" t="n">
+        <v>19351</v>
       </c>
       <c r="M502" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N502" s="3" t="inlineStr">
@@ -33968,7 +33336,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -33976,34 +33344,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H503" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I503" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H503" s="5" t="n">
+        <v>6936000</v>
+      </c>
+      <c r="I503" s="5" t="n">
+        <v>21743</v>
       </c>
       <c r="J503" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K503" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L503" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K503" s="5" t="n">
+        <v>6173040</v>
+      </c>
+      <c r="L503" s="5" t="n">
+        <v>19351</v>
       </c>
       <c r="M503" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N503" s="3" t="inlineStr">
@@ -34038,7 +33398,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -34046,34 +33406,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H504" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I504" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H504" s="5" t="n">
+        <v>6763000</v>
+      </c>
+      <c r="I504" s="5" t="n">
+        <v>21746</v>
       </c>
       <c r="J504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K504" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L504" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K504" s="5" t="n">
+        <v>6019070</v>
+      </c>
+      <c r="L504" s="5" t="n">
+        <v>19354</v>
       </c>
       <c r="M504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N504" s="3" t="inlineStr">
@@ -34108,7 +33460,7 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -34116,34 +33468,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H505" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I505" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H505" s="5" t="n">
+        <v>7125000</v>
+      </c>
+      <c r="I505" s="5" t="n">
+        <v>21591</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K505" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L505" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K505" s="5" t="n">
+        <v>6341250</v>
+      </c>
+      <c r="L505" s="5" t="n">
+        <v>19216</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N505" s="3" t="inlineStr">
@@ -34458,7 +33802,7 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -34466,34 +33810,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H510" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I510" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H510" s="5" t="n">
+        <v>7113000</v>
+      </c>
+      <c r="I510" s="5" t="n">
+        <v>22090</v>
       </c>
       <c r="J510" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K510" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L510" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K510" s="5" t="n">
+        <v>6330570</v>
+      </c>
+      <c r="L510" s="5" t="n">
+        <v>19660</v>
       </c>
       <c r="M510" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N510" s="3" t="inlineStr">
@@ -34528,7 +33864,7 @@
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G511" s="3" t="inlineStr">
@@ -34536,34 +33872,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H511" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I511" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H511" s="5" t="n">
+        <v>5302000</v>
+      </c>
+      <c r="I511" s="5" t="n">
+        <v>21293</v>
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K511" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L511" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K511" s="5" t="n">
+        <v>4718780</v>
+      </c>
+      <c r="L511" s="5" t="n">
+        <v>18951</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N511" s="3" t="inlineStr">
@@ -34598,7 +33926,7 @@
       </c>
       <c r="F512" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G512" s="3" t="inlineStr">
@@ -34606,34 +33934,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H512" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I512" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H512" s="5" t="n">
+        <v>6815000</v>
+      </c>
+      <c r="I512" s="5" t="n">
+        <v>21364</v>
       </c>
       <c r="J512" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K512" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L512" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K512" s="5" t="n">
+        <v>6065350</v>
+      </c>
+      <c r="L512" s="5" t="n">
+        <v>19014</v>
       </c>
       <c r="M512" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N512" s="3" t="inlineStr">
@@ -34668,7 +33988,7 @@
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
@@ -34676,34 +33996,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H513" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I513" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H513" s="5" t="n">
+        <v>6815000</v>
+      </c>
+      <c r="I513" s="5" t="n">
+        <v>21364</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K513" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L513" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K513" s="5" t="n">
+        <v>6065350</v>
+      </c>
+      <c r="L513" s="5" t="n">
+        <v>19014</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N513" s="3" t="inlineStr">
@@ -34738,7 +34050,7 @@
       </c>
       <c r="F514" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G514" s="3" t="inlineStr">
@@ -34746,34 +34058,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H514" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I514" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H514" s="5" t="n">
+        <v>6644000</v>
+      </c>
+      <c r="I514" s="5" t="n">
+        <v>21363</v>
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K514" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L514" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K514" s="5" t="n">
+        <v>5913160</v>
+      </c>
+      <c r="L514" s="5" t="n">
+        <v>19013</v>
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N514" s="3" t="inlineStr">
@@ -34808,7 +34112,7 @@
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr">
@@ -34816,34 +34120,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H515" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I515" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H515" s="5" t="n">
+        <v>7001000</v>
+      </c>
+      <c r="I515" s="5" t="n">
+        <v>21215</v>
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K515" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L515" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K515" s="5" t="n">
+        <v>6230890</v>
+      </c>
+      <c r="L515" s="5" t="n">
+        <v>18881</v>
       </c>
       <c r="M515" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N515" s="3" t="inlineStr">
@@ -34878,7 +34174,7 @@
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G516" s="3" t="inlineStr">
@@ -34886,34 +34182,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H516" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I516" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H516" s="5" t="n">
+        <v>8233000</v>
+      </c>
+      <c r="I516" s="5" t="n">
+        <v>24215</v>
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K516" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L516" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K516" s="5" t="n">
+        <v>7327370</v>
+      </c>
+      <c r="L516" s="5" t="n">
+        <v>21551</v>
       </c>
       <c r="M516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N516" s="3" t="inlineStr">
@@ -35158,7 +34446,7 @@
       </c>
       <c r="F520" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G520" s="3" t="inlineStr">
@@ -35166,34 +34454,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H520" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I520" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H520" s="5" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="I520" s="5" t="n">
+        <v>22034</v>
       </c>
       <c r="J520" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K520" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L520" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K520" s="5" t="n">
+        <v>6314550</v>
+      </c>
+      <c r="L520" s="5" t="n">
+        <v>19610</v>
       </c>
       <c r="M520" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N520" s="3" t="inlineStr">
@@ -35228,7 +34508,7 @@
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G521" s="3" t="inlineStr">
@@ -35236,34 +34516,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H521" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I521" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H521" s="5" t="n">
+        <v>5183000</v>
+      </c>
+      <c r="I521" s="5" t="n">
+        <v>20815</v>
       </c>
       <c r="J521" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K521" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L521" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K521" s="5" t="n">
+        <v>4612870</v>
+      </c>
+      <c r="L521" s="5" t="n">
+        <v>18526</v>
       </c>
       <c r="M521" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N521" s="3" t="inlineStr">
@@ -35298,7 +34570,7 @@
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
@@ -35306,34 +34578,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H522" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I522" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H522" s="5" t="n">
+        <v>6662000</v>
+      </c>
+      <c r="I522" s="5" t="n">
+        <v>20884</v>
       </c>
       <c r="J522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K522" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L522" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K522" s="5" t="n">
+        <v>5929180</v>
+      </c>
+      <c r="L522" s="5" t="n">
+        <v>18587</v>
       </c>
       <c r="M522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N522" s="3" t="inlineStr">
@@ -35368,7 +34632,7 @@
       </c>
       <c r="F523" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G523" s="3" t="inlineStr">
@@ -35376,34 +34640,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H523" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I523" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H523" s="5" t="n">
+        <v>6662000</v>
+      </c>
+      <c r="I523" s="5" t="n">
+        <v>20884</v>
       </c>
       <c r="J523" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K523" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L523" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K523" s="5" t="n">
+        <v>5929180</v>
+      </c>
+      <c r="L523" s="5" t="n">
+        <v>18587</v>
       </c>
       <c r="M523" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N523" s="3" t="inlineStr">
@@ -35438,7 +34694,7 @@
       </c>
       <c r="F524" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
@@ -35446,34 +34702,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H524" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I524" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H524" s="5" t="n">
+        <v>6495000</v>
+      </c>
+      <c r="I524" s="5" t="n">
+        <v>20884</v>
       </c>
       <c r="J524" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K524" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L524" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K524" s="5" t="n">
+        <v>5780550</v>
+      </c>
+      <c r="L524" s="5" t="n">
+        <v>18587</v>
       </c>
       <c r="M524" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N524" s="3" t="inlineStr">
@@ -37711,7 +36959,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -37726,7 +36974,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -37802,52 +37050,52 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>C | 330呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
+$776万
+$23,506/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
+$736万
+$23,669/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G5" s="22" t="inlineStr">
+$755万
+$23,671/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>F | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
+$759万
+$23,790/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I5" s="22" t="inlineStr">
+$588万
+$23,594/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$776万
+$24,106/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -37889,52 +37137,52 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 330呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
+$774万
+$23,445/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
+$734万
+$23,611/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="22" t="inlineStr">
+$753万
+$23,611/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
+$757万
+$23,730/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="22" t="inlineStr">
+$586万
+$23,534/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$774万
+$24,047/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -37976,52 +37224,52 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 330呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+$770万
+$23,330/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
+$731万
+$23,495/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
+$750万
+$23,495/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
+$753万
+$23,611/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="22" t="inlineStr">
+$583万
+$23,418/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$770万
+$23,925/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -38071,12 +37319,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$729万
+$23,434/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -38103,12 +37351,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$768万
+$23,866/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -38158,12 +37406,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$727万
+$23,376/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -38190,12 +37438,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$767万
+$23,807/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -38245,12 +37493,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$725万
+$23,318/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -38277,12 +37525,12 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$765万
+$23,748/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -38332,12 +37580,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$723万
+$23,260/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -38364,12 +37612,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$763万
+$23,689/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -38419,12 +37667,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$722万
+$23,203/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -38451,12 +37699,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$761万
+$23,630/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -38506,12 +37754,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$720万
+$23,145/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -38538,12 +37786,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$759万
+$23,571/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -38593,12 +37841,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$718万
+$23,087/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -38625,12 +37873,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$757万
+$23,512/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -38672,52 +37920,52 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 330呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
+$755万
+$22,867/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+$716万
+$23,029/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+$735万
+$23,028/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>F | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
+$738万
+$23,144/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
+$572万
+$22,952/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$755万
+$23,453/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -38767,12 +38015,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$713万
+$22,913/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -38799,12 +38047,12 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$751万
+$23,335/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -38854,12 +38102,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$711万
+$22,859/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -38886,12 +38134,12 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$750万
+$23,280/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -38941,12 +38189,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$709万
+$22,801/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -38973,12 +38221,12 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$748万
+$23,220/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -39028,12 +38276,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$707万
+$22,743/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -39060,12 +38308,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$746万
+$23,161/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -39115,12 +38363,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$706万
+$22,688/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -39147,12 +38395,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$744万
+$23,106/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -39202,12 +38450,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$704万
+$22,630/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -39234,12 +38482,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$742万
+$23,047/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -39289,12 +38537,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$702万
+$22,576/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -39321,12 +38569,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$740万
+$22,991/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -39376,12 +38624,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$700万
+$22,518/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -39408,12 +38656,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$738万
+$22,932/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -39463,12 +38711,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$699万
+$22,463/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -39495,12 +38743,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$737万
+$22,876/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -39550,12 +38798,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$695万
+$22,350/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -39582,12 +38830,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$733万
+$22,761/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -39637,12 +38885,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$693万
+$22,293/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -39669,12 +38917,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$731万
+$22,705/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -39724,12 +38972,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$692万
+$22,238/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -39756,12 +39004,12 @@
 (26年-01月-14日)</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$729万
+$22,649/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -39811,12 +39059,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$690万
+$22,183/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -39843,12 +39091,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$728万
+$22,593/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -39898,12 +39146,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$688万
+$22,129/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -39930,12 +39178,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$726万
+$22,534/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -39985,12 +39233,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$686万
+$22,074/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -40017,12 +39265,12 @@
 (26年-01月-08日)</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$724万
+$22,478/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -40072,12 +39320,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$685万
+$22,016/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -40104,12 +39352,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$722万
+$22,422/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -40159,12 +39407,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$683万
+$21,961/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -40191,12 +39439,12 @@
 (26年-01月-14日)</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$720万
+$22,366/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -40246,12 +39494,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$680万
+$21,852/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -40278,12 +39526,12 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$717万
+$22,255/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -40333,12 +39581,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
+$678万
+$21,797/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -40365,12 +39613,12 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$715万
+$22,202/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -40412,52 +39660,52 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 330呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
+$712万
+$21,591/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="22" t="inlineStr">
+$676万
+$21,746/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr">
+$694万
+$21,743/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>F | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H35" s="22" t="inlineStr">
+$694万
+$21,743/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I35" s="22" t="inlineStr">
+$540万
+$21,675/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$713万
+$22,146/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -40491,60 +39739,60 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 340呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="22" t="inlineStr">
+$823万
+$24,215/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>C | 330呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="22" t="inlineStr">
+$700万
+$21,215/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
+$664万
+$21,363/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr">
+$682万
+$21,364/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
         <is>
           <t>F | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H36" s="22" t="inlineStr">
+$682万
+$21,364/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I36" s="22" t="inlineStr">
+$530万
+$21,293/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$711万
+$22,090/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -40594,44 +39842,44 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="inlineStr">
+$650万
+$20,884/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr">
+$666万
+$20,884/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>F | 319呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
+$666万
+$20,884/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I37" s="22" t="inlineStr">
+$518万
+$20,815/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
--
--
-(待售)</t>
+$710万
+$22,034/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -3087,38 +3087,30 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>18120000</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>26034</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K36" s="5" t="n">
+        <v>18120000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>26034</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3127,7 +3119,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4797,38 +4789,30 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>16059000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>25053</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K61" s="5" t="n">
+        <v>16059000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>25053</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4837,7 +4821,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35055,7 +35039,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35065,7 +35049,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35398,7 +35382,62 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+$1812万
+$26,034/呎
+(26年-09月-13日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 430呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 696呎 (3房)
 招标单位
@@ -35406,7 +35445,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 518呎 (2房)
 -
@@ -35414,7 +35453,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 436呎 (2房)
 -
@@ -35422,7 +35461,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 429呎 (2房)
 招标单位
@@ -35430,7 +35469,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 430呎 (2房)
 招标单位
@@ -35439,29 +35478,29 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
-招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 696呎 (3房)
-招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 518呎 (2房)
 -
@@ -35469,7 +35508,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 436呎 (2房)
 -
@@ -35477,7 +35516,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 429呎 (2房)
 招标单位
@@ -35485,22 +35524,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>F | 430呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$791万
+$18,346/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
 -
@@ -35508,15 +35547,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 695呎 (3房)
+$1631万
+$23,471/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 518呎 (2房)
 -
@@ -35524,7 +35563,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 436呎 (2房)
 -
@@ -35532,7 +35571,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 429呎 (2房)
 招标单位
@@ -35540,61 +35579,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$791万
-$18,346/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 695呎 (3房)
-$1631万
-$23,471/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 431呎 (2房)
@@ -35610,12 +35594,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
-招标单位
--
-(在售)</t>
+$1606万
+$25,053/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -4113,38 +4113,30 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>8953000</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>20869</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K51" s="5" t="n">
+        <v>8953000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>20869</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -4153,7 +4145,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12785,38 +12777,30 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I183" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>8155000</v>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>19009</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K183" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L183" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K183" s="5" t="n">
+        <v>8155000</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>19009</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
@@ -12825,7 +12809,7 @@
       </c>
       <c r="N183" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14091,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14689,7 +14673,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -15341,7 +15325,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -21967,7 +21951,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -22603,7 +22587,7 @@
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -23239,34 +23223,34 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
-        <v>7073000</v>
+        <v>6295000</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>22743</v>
+        <v>20241</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K344" s="5" t="n">
-        <v>6294970</v>
+        <v>6295000</v>
       </c>
       <c r="L344" s="5" t="n">
         <v>20241</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N344" s="3" t="inlineStr">
@@ -23875,7 +23859,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -24511,7 +24495,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -25147,7 +25131,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -25783,7 +25767,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -26419,7 +26403,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -27055,7 +27039,7 @@
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -27691,7 +27675,7 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -28327,7 +28311,7 @@
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
@@ -28963,7 +28947,7 @@
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -29599,7 +29583,7 @@
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr">
@@ -30235,7 +30219,7 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
@@ -30871,7 +30855,7 @@
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G464" s="3" t="inlineStr">
@@ -31507,7 +31491,7 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -32143,7 +32127,7 @@
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
@@ -32779,7 +32763,7 @@
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
@@ -33237,34 +33221,34 @@
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
-        <v>5397000</v>
+        <v>4804000</v>
       </c>
       <c r="I501" s="5" t="n">
-        <v>21675</v>
+        <v>19293</v>
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K501" s="5" t="n">
-        <v>4803330</v>
+        <v>4804000</v>
       </c>
       <c r="L501" s="5" t="n">
-        <v>19290</v>
+        <v>19293</v>
       </c>
       <c r="M501" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N501" s="3" t="inlineStr">
@@ -33361,7 +33345,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -33423,7 +33407,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -33889,34 +33873,34 @@
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
-        <v>5302000</v>
+        <v>4719000</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>21293</v>
+        <v>18952</v>
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K511" s="5" t="n">
-        <v>4718780</v>
+        <v>4719000</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>18951</v>
+        <v>18952</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N511" s="3" t="inlineStr">
@@ -34013,7 +33997,7 @@
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
@@ -34075,7 +34059,7 @@
       </c>
       <c r="F514" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G514" s="3" t="inlineStr">
@@ -34533,34 +34517,34 @@
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
-        <v>5183000</v>
+        <v>4613000</v>
       </c>
       <c r="I521" s="5" t="n">
-        <v>20815</v>
+        <v>18526</v>
       </c>
       <c r="J521" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K521" s="5" t="n">
-        <v>4612870</v>
+        <v>4613000</v>
       </c>
       <c r="L521" s="5" t="n">
         <v>18526</v>
       </c>
       <c r="M521" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N521" s="3" t="inlineStr">
@@ -34657,7 +34641,7 @@
       </c>
       <c r="F523" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G523" s="3" t="inlineStr">
@@ -34719,7 +34703,7 @@
       </c>
       <c r="F524" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
@@ -35039,7 +35023,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35049,7 +35033,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35571,12 +35555,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 429呎 (2房)
-招标单位
--
-(在售)</t>
+$895万
+$20,869/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -36781,12 +36765,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 429呎 (2房)
-招标单位
--
-(在售)</t>
+$816万
+$19,009/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -36979,17 +36963,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37107,12 +37091,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
 $588万
 $23,594/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I5" s="24" t="inlineStr">
@@ -37194,12 +37178,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
 $586万
 $23,534/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">
@@ -37281,12 +37265,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
 $583万
 $23,418/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I7" s="24" t="inlineStr">
@@ -38127,12 +38111,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $711万
 $22,859/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -38214,12 +38198,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $709万
 $22,801/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -38301,12 +38285,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$707万
-$22,743/呎
-(已定价未售)</t>
+$630万
+$20,241/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -38388,12 +38372,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $706万
 $22,688/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -38475,12 +38459,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $704万
 $22,630/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -38562,12 +38546,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $702万
 $22,576/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -38649,12 +38633,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $700万
 $22,518/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -38736,12 +38720,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $699万
 $22,463/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -38823,12 +38807,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $695万
 $22,350/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -38910,12 +38894,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $693万
 $22,293/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -38997,12 +38981,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $692万
 $22,238/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -39084,12 +39068,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $690万
 $22,183/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -39171,12 +39155,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $688万
 $22,129/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -39258,12 +39242,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $686万
 $22,074/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -39345,12 +39329,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $685万
 $22,016/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -39432,12 +39416,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $683万
 $21,961/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -39519,12 +39503,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $680万
 $21,852/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F33" s="25" t="inlineStr">
@@ -39606,12 +39590,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $678万
 $21,797/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -39693,20 +39677,20 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $676万
 $21,746/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $694万
 $21,743/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
@@ -39717,12 +39701,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H35" s="24" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
-$540万
-$21,675/呎
-(已定价未售)</t>
+$480万
+$19,293/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="I35" s="24" t="inlineStr">
@@ -39780,20 +39764,20 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $664万
 $21,363/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $682万
 $21,364/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
@@ -39804,12 +39788,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H36" s="24" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
-$530万
-$21,293/呎
-(已定价未售)</t>
+$472万
+$18,952/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="I36" s="24" t="inlineStr">
@@ -39867,20 +39851,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $650万
 $20,884/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $666万
 $20,884/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
@@ -39891,12 +39875,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H37" s="24" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
-$518万
-$20,815/呎
-(已定价未售)</t>
+$461万
+$18,526/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="I37" s="24" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>16059000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>25053</v>
+        <v>25092</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>16059000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>25053</v>
+        <v>25092</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         </is>
       </c>
       <c r="E511" s="4" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>4719000</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>18952</v>
+        <v>18876</v>
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>4719000</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>18952</v>
+        <v>18876</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
@@ -35580,9 +35580,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 641呎 (3房)
+          <t>A | 640呎 (3房)
 $1606万
-$25,053/呎
+$25,092/呎
 (26年-09月-13日)</t>
         </is>
       </c>
@@ -39790,9 +39790,9 @@
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
-          <t>G | 249呎 (开放式)
+          <t>G | 250呎 (开放式)
 $472万
-$18,952/呎
+$18,876/呎
 (26年-09月-16日)</t>
         </is>
       </c>

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -4711,38 +4711,30 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>17938000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>25773</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K60" s="5" t="n">
+        <v>17938000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>25773</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4751,7 +4743,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5977,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -5995,12 +5987,12 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -6010,12 +6002,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -6025,7 +6017,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24239,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -24883,7 +24875,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -25519,7 +25511,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -26791,7 +26783,7 @@
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -27427,7 +27419,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -28063,7 +28055,7 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -35033,7 +35025,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35043,7 +35035,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -35586,12 +35578,12 @@
 (26年-09月-13日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 696呎 (3房)
-招标单位
--
-(在售)</t>
+$1794万
+$25,773/呎
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -35743,12 +35735,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -36963,12 +36955,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -38491,12 +38483,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $742万
 $23,047/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -38578,12 +38570,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $740万
 $22,991/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -38665,12 +38657,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $738万
 $22,932/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -38839,12 +38831,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $733万
 $22,761/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -38926,12 +38918,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $731万
 $22,705/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -39013,12 +39005,12 @@
 (26年-01月-14日)</t>
         </is>
       </c>
-      <c r="I27" s="24" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $729万
 $22,649/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -5977,38 +5977,30 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>15899000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>24803</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K79" s="5" t="n">
+        <v>15899000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>24803</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6017,7 +6009,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15317,34 +15309,34 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>5831000</v>
+        <v>5190000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>23418</v>
+        <v>20843</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>5189590</v>
+        <v>5190000</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>20842</v>
+        <v>20843</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -19127,34 +19119,34 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
-        <v>7590000</v>
+        <v>6756000</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>23571</v>
+        <v>20981</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K280" s="5" t="n">
-        <v>6755100</v>
+        <v>6756000</v>
       </c>
       <c r="L280" s="5" t="n">
-        <v>20979</v>
+        <v>20981</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
@@ -19771,7 +19763,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -22331,7 +22323,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -22967,7 +22959,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -24239,34 +24231,34 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
-        <v>7421000</v>
+        <v>6605000</v>
       </c>
       <c r="I360" s="5" t="n">
-        <v>23047</v>
+        <v>20512</v>
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>6604690</v>
+        <v>6605000</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>20511</v>
+        <v>20512</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -25511,34 +25503,34 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
-        <v>7384000</v>
+        <v>6572000</v>
       </c>
       <c r="I380" s="5" t="n">
-        <v>22932</v>
+        <v>20410</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K380" s="5" t="n">
-        <v>6571760</v>
+        <v>6572000</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>20409</v>
+        <v>20410</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N380" s="3" t="inlineStr">
@@ -27031,34 +27023,34 @@
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
-        <v>6951000</v>
+        <v>6187000</v>
       </c>
       <c r="I404" s="5" t="n">
-        <v>22350</v>
+        <v>19894</v>
       </c>
       <c r="J404" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K404" s="5" t="n">
-        <v>6186390</v>
+        <v>6187000</v>
       </c>
       <c r="L404" s="5" t="n">
-        <v>19892</v>
+        <v>19894</v>
       </c>
       <c r="M404" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N404" s="3" t="inlineStr">
@@ -30211,34 +30203,34 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
-        <v>6865000</v>
+        <v>6179000</v>
       </c>
       <c r="I454" s="5" t="n">
-        <v>22074</v>
+        <v>19868</v>
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>6109850</v>
+        <v>6179000</v>
       </c>
       <c r="L454" s="5" t="n">
-        <v>19646</v>
+        <v>19868</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -35015,7 +35007,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35025,7 +35017,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35735,12 +35727,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
-招标单位
--
-(在售)</t>
+$1590万
+$24,803/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -36955,17 +36947,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>157</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37257,12 +37249,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
-$583万
-$23,418/呎
-(在售)</t>
+$519万
+$20,843/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="I7" s="24" t="inlineStr">
@@ -37787,12 +37779,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$759万
-$23,571/呎
-(已定价未售)</t>
+$676万
+$20,981/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -37874,12 +37866,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $757万
 $23,512/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -38222,12 +38214,12 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $748万
 $23,220/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -38309,12 +38301,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $746万
 $23,161/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -38483,12 +38475,12 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="I21" s="23" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$742万
-$23,047/呎
-(在售)</t>
+$660万
+$20,512/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -38657,12 +38649,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$738万
-$22,932/呎
-(在售)</t>
+$657万
+$20,410/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -38799,12 +38791,12 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$695万
-$22,350/呎
-(在售)</t>
+$619万
+$19,894/呎
+(26年-10月-04日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -39234,12 +39226,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$686万
-$22,074/呎
-(在售)</t>
+$618万
+$19,868/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -3219,38 +3219,30 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>8748000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>20344</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K38" s="5" t="n">
+        <v>8748000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>20344</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3259,7 +3251,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12551,38 +12543,30 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>16936000</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>24333</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L180" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K180" s="5" t="n">
+        <v>16936000</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>24333</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -12591,7 +12575,7 @@
       </c>
       <c r="N180" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12750,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -14657,34 +14641,34 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>5860000</v>
+        <v>5216000</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>23534</v>
+        <v>20948</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K211" s="5" t="n">
-        <v>5215400</v>
+        <v>5216000</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>20945</v>
+        <v>20948</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
@@ -35007,7 +34991,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35017,7 +35001,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35437,12 +35421,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 430呎 (2房)
-招标单位
--
-(在售)</t>
+$875万
+$20,344/呎
+(26年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -36670,7 +36654,62 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 696呎 (3房)
+$1694万
+$24,333/呎
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 518呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 429呎 (2房)
+$756万
+$17,611/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 431呎 (2房)
+$743万
+$17,234/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>A | 641呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 696呎 (3房)
 招标单位
@@ -36678,7 +36717,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 518呎 (2房)
 -
@@ -36686,7 +36725,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 436呎 (2房)
 -
@@ -36694,67 +36733,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>E | 429呎 (2房)
-$756万
-$17,611/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>F | 431呎 (2房)
-$743万
-$17,234/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>A | 641呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>B | 696呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="inlineStr">
-        <is>
-          <t>C | 518呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>D | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 429呎 (2房)
 $816万
 $19,009/呎
-(26年-09月-16日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -36947,7 +36931,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -36957,7 +36941,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37162,12 +37146,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
-$586万
-$23,534/呎
-(在售)</t>
+$522万
+$20,948/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3092,14 +3092,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
         <v>18120000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>26034</v>
+        <v>26072</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>18120000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>26034</v>
+        <v>26072</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>8748000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>20344</v>
+        <v>20297</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>8748000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>20344</v>
+        <v>20297</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -12675,38 +12675,30 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>8108000</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>18856</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L182" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K182" s="5" t="n">
+        <v>8108000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>18856</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -12715,7 +12707,7 @@
       </c>
       <c r="N182" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23196,7 +23188,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -28031,34 +28023,34 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
-        <v>7293000</v>
+        <v>6491000</v>
       </c>
       <c r="I420" s="5" t="n">
-        <v>22649</v>
+        <v>20158</v>
       </c>
       <c r="J420" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K420" s="5" t="n">
-        <v>6490770</v>
+        <v>6491000</v>
       </c>
       <c r="L420" s="5" t="n">
         <v>20158</v>
       </c>
       <c r="M420" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N420" s="3" t="inlineStr">
@@ -32731,34 +32723,34 @@
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
-        <v>6779000</v>
+        <v>6034000</v>
       </c>
       <c r="I494" s="5" t="n">
-        <v>21797</v>
+        <v>19402</v>
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K494" s="5" t="n">
-        <v>6033310</v>
+        <v>6034000</v>
       </c>
       <c r="L494" s="5" t="n">
-        <v>19400</v>
+        <v>19402</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N494" s="3" t="inlineStr">
@@ -33185,7 +33177,7 @@
         </is>
       </c>
       <c r="E501" s="4" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
@@ -33194,14 +33186,14 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
         <v>4804000</v>
       </c>
       <c r="I501" s="5" t="n">
-        <v>19293</v>
+        <v>19216</v>
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
@@ -33212,7 +33204,7 @@
         <v>4804000</v>
       </c>
       <c r="L501" s="5" t="n">
-        <v>19293</v>
+        <v>19216</v>
       </c>
       <c r="M501" s="3" t="inlineStr">
         <is>
@@ -33499,38 +33491,30 @@
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H506" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I506" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H506" s="5" t="n">
+        <v>10082000</v>
+      </c>
+      <c r="I506" s="5" t="n">
+        <v>22158</v>
       </c>
       <c r="J506" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K506" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L506" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K506" s="5" t="n">
+        <v>10082000</v>
+      </c>
+      <c r="L506" s="5" t="n">
+        <v>22158</v>
       </c>
       <c r="M506" s="3" t="inlineStr">
         <is>
@@ -33539,7 +33523,7 @@
       </c>
       <c r="N506" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -34481,7 +34465,7 @@
         </is>
       </c>
       <c r="E521" s="4" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
@@ -34490,14 +34474,14 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
         <v>4613000</v>
       </c>
       <c r="I521" s="5" t="n">
-        <v>18526</v>
+        <v>18452</v>
       </c>
       <c r="J521" s="3" t="inlineStr">
         <is>
@@ -34508,7 +34492,7 @@
         <v>4613000</v>
       </c>
       <c r="L521" s="5" t="n">
-        <v>18526</v>
+        <v>18452</v>
       </c>
       <c r="M521" s="3" t="inlineStr">
         <is>
@@ -34991,7 +34975,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -35001,7 +34985,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35336,10 +35320,10 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 696呎 (3房)
+          <t>B | 695呎 (3房)
 $1812万
-$26,034/呎
-(26年-09月-13日)</t>
+$26,072/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -35423,9 +35407,9 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 430呎 (2房)
+          <t>F | 431呎 (2房)
 $875万
-$20,344/呎
+$20,297/呎
 (26年-10月-05日)</t>
         </is>
       </c>
@@ -35528,7 +35512,7 @@
           <t>E | 429呎 (2房)
 $895万
 $20,869/呎
-(26年-09月-16日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -35551,7 +35535,7 @@
           <t>A | 640呎 (3房)
 $1606万
 $25,092/呎
-(26年-09月-13日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -36741,12 +36725,12 @@
 (26年-10月-08日)</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 430呎 (2房)
-招标单位
--
-(在售)</t>
+$811万
+$18,856/呎
+(26年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -36931,7 +36915,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -36941,7 +36925,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -38258,7 +38242,7 @@
           <t>D | 311呎 (1房)
 $630万
 $20,241/呎
-(26年-09月-16日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -38981,12 +38965,12 @@
 (26年-01月-14日)</t>
         </is>
       </c>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$729万
-$22,649/呎
-(在售)</t>
+$649万
+$20,158/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -39558,12 +39542,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$678万
-$21,797/呎
-(在售)</t>
+$603万
+$19,402/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -39629,12 +39613,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 455呎 (2房)
-招标单位
--
-(在售)</t>
+$1008万
+$22,158/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
@@ -39671,10 +39655,10 @@
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>G | 249呎 (开放式)
+          <t>G | 250呎 (开放式)
 $480万
-$19,293/呎
-(26年-09月-16日)</t>
+$19,216/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="I35" s="24" t="inlineStr">
@@ -39845,10 +39829,10 @@
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>G | 249呎 (开放式)
+          <t>G | 250呎 (开放式)
 $461万
-$18,526/呎
-(26年-09月-16日)</t>
+$18,452/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="I37" s="24" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -33830,7 +33830,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -39745,7 +39745,7 @@
           <t>G | 250呎 (开放式)
 $472万
 $18,876/呎
-(26年-09月-16日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="I36" s="24" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3491,38 +3491,30 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>18072000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>25966</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K42" s="5" t="n">
+        <v>18072000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>25966</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3531,7 +3523,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7157,38 +7149,30 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>15780000</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>24618</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K97" s="5" t="n">
+        <v>15780000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>24618</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -7197,7 +7181,7 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14051,34 +14035,34 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
-        <v>5875000</v>
+        <v>5288000</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>23594</v>
+        <v>21237</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K202" s="5" t="n">
-        <v>5228750</v>
+        <v>5288000</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>20999</v>
+        <v>21237</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N202" s="3" t="inlineStr">
@@ -18179,7 +18163,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -18189,12 +18173,12 @@
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I266" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J266" s="3" t="inlineStr">
@@ -18204,12 +18188,12 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
@@ -18219,7 +18203,7 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18478,7 +18462,7 @@
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
@@ -18823,7 +18807,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -18833,12 +18817,12 @@
       </c>
       <c r="H276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J276" s="3" t="inlineStr">
@@ -18848,12 +18832,12 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
@@ -18863,7 +18847,7 @@
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19467,38 +19451,30 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="n">
+        <v>10732000</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>23587</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K286" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K286" s="5" t="n">
+        <v>10732000</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>23587</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
@@ -19507,7 +19483,7 @@
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19739,34 +19715,34 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
-        <v>7571000</v>
+        <v>6739000</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>23512</v>
+        <v>20929</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K290" s="5" t="n">
-        <v>6738190</v>
+        <v>6739000</v>
       </c>
       <c r="L290" s="5" t="n">
-        <v>20926</v>
+        <v>20929</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N290" s="3" t="inlineStr">
@@ -21054,7 +21030,7 @@
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N310" s="3" t="inlineStr">
@@ -21690,7 +21666,7 @@
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N320" s="3" t="inlineStr">
@@ -21938,7 +21914,7 @@
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N324" s="3" t="inlineStr">
@@ -22299,34 +22275,34 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
-        <v>7477000</v>
+        <v>6655000</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>23220</v>
+        <v>20668</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>6654530</v>
+        <v>6655000</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>20666</v>
+        <v>20668</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -22574,7 +22550,7 @@
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N334" s="3" t="inlineStr">
@@ -22935,34 +22911,34 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
-        <v>7458000</v>
+        <v>6638000</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>23161</v>
+        <v>20615</v>
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K340" s="5" t="n">
-        <v>6637620</v>
+        <v>6638000</v>
       </c>
       <c r="L340" s="5" t="n">
-        <v>20614</v>
+        <v>20615</v>
       </c>
       <c r="M340" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N340" s="3" t="inlineStr">
@@ -23598,7 +23574,7 @@
       </c>
       <c r="M350" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N350" s="3" t="inlineStr">
@@ -23846,7 +23822,7 @@
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N354" s="3" t="inlineStr">
@@ -24212,7 +24188,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -24482,7 +24458,7 @@
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N364" s="3" t="inlineStr">
@@ -24843,34 +24819,34 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
-        <v>7403000</v>
+        <v>6589000</v>
       </c>
       <c r="I370" s="5" t="n">
-        <v>22991</v>
+        <v>20463</v>
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>6588670</v>
+        <v>6589000</v>
       </c>
       <c r="L370" s="5" t="n">
-        <v>20462</v>
+        <v>20463</v>
       </c>
       <c r="M370" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N370" s="3" t="inlineStr">
@@ -25118,7 +25094,7 @@
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N374" s="3" t="inlineStr">
@@ -25484,7 +25460,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -25754,7 +25730,7 @@
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -26142,7 +26118,7 @@
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -26390,7 +26366,7 @@
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -27004,7 +26980,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -27387,34 +27363,34 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
-        <v>7311000</v>
+        <v>6507000</v>
       </c>
       <c r="I410" s="5" t="n">
-        <v>22705</v>
+        <v>20208</v>
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K410" s="5" t="n">
-        <v>6506790</v>
+        <v>6507000</v>
       </c>
       <c r="L410" s="5" t="n">
-        <v>20207</v>
+        <v>20208</v>
       </c>
       <c r="M410" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N410" s="3" t="inlineStr">
@@ -27662,7 +27638,7 @@
       </c>
       <c r="M414" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N414" s="3" t="inlineStr">
@@ -28298,7 +28274,7 @@
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N424" s="3" t="inlineStr">
@@ -28934,7 +28910,7 @@
       </c>
       <c r="M434" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N434" s="3" t="inlineStr">
@@ -29570,7 +29546,7 @@
       </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N444" s="3" t="inlineStr">
@@ -30184,7 +30160,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -30842,7 +30818,7 @@
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N464" s="3" t="inlineStr">
@@ -31451,7 +31427,7 @@
       </c>
       <c r="F474" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G474" s="3" t="inlineStr">
@@ -31478,7 +31454,7 @@
       </c>
       <c r="M474" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N474" s="3" t="inlineStr">
@@ -32087,7 +32063,7 @@
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr">
@@ -32114,7 +32090,7 @@
       </c>
       <c r="M484" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N484" s="3" t="inlineStr">
@@ -33332,7 +33308,7 @@
       </c>
       <c r="M503" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N503" s="3" t="inlineStr">
@@ -33367,7 +33343,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -33394,7 +33370,7 @@
       </c>
       <c r="M504" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N504" s="3" t="inlineStr">
@@ -33976,7 +33952,7 @@
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N513" s="3" t="inlineStr">
@@ -34011,7 +33987,7 @@
       </c>
       <c r="F514" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G514" s="3" t="inlineStr">
@@ -34038,7 +34014,7 @@
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N514" s="3" t="inlineStr">
@@ -34620,7 +34596,7 @@
       </c>
       <c r="M523" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N523" s="3" t="inlineStr">
@@ -34655,7 +34631,7 @@
       </c>
       <c r="F524" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
@@ -34682,7 +34658,7 @@
       </c>
       <c r="M524" s="3" t="inlineStr">
         <is>
-          <t>優先進駐90天現金優惠付款計劃</t>
+          <t>醫護專享120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N524" s="3" t="inlineStr">
@@ -34975,7 +34951,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -34985,7 +34961,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35373,12 +35349,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 696呎 (3房)
-招标单位
--
-(在售)</t>
+$1807万
+$25,966/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -35410,7 +35386,7 @@
           <t>F | 431呎 (2房)
 $875万
 $20,297/呎
-(26年-10月-05日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -35860,12 +35836,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
-招标单位
--
-(在售)</t>
+$1578万
+$24,618/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -36915,7 +36891,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -36925,17 +36901,17 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -37043,12 +37019,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 249呎 (开放式)
-$588万
-$23,594/呎
-(在售)</t>
+$529万
+$21,237/呎
+(26年-10月-17日)</t>
         </is>
       </c>
       <c r="I5" s="24" t="inlineStr">
@@ -37525,7 +37501,355 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$629万
+$19,109/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$723万
+$23,260/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$617万
+$19,291/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$622万
+$19,438/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$475万
+$18,996/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$763万
+$23,689/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$825万
+$19,920/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$627万
+$19,061/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$722万
+$23,203/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$616万
+$19,241/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$614万
+$19,175/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$474万
+$18,948/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$761万
+$23,630/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$823万
+$19,872/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1073万
+$23,587/呎
+(26年-10月-17日)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$626万
+$19,015/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$720万
+$23,145/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$613万
+$19,156/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$583万
+$18,219/呎
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$473万
+$18,904/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$676万
+$20,981/呎
+(26年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$820万
+$19,819/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$962万
+$21,198/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$624万
+$18,967/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$718万
+$23,087/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$611万
+$19,106/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$582万
+$18,172/呎
+(26年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$471万
+$18,852/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$674万
+$20,929/呎
+(26年-10月-16日)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$818万
+$19,771/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>K | 423呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 468呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 455呎 (2房)
 -
@@ -37533,63 +37857,63 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$629万
-$19,109/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+$755万
+$22,867/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$723万
-$23,260/呎
+$716万
+$23,029/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$617万
-$19,291/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$622万
-$19,438/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$475万
-$18,996/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+$735万
+$23,028/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+$738万
+$23,144/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+$572万
+$22,952/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$763万
-$23,689/呎
+$755万
+$23,453/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$825万
-$19,920/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="K11" s="22" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -37598,13 +37922,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -37612,71 +37936,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$955万
+$21,040/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$627万
-$19,061/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
+$619万
+$18,827/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$722万
-$23,203/呎
+$713万
+$22,913/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$616万
-$19,241/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
+$607万
+$18,966/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$614万
-$19,175/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
+$577万
+$18,038/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$474万
-$18,948/呎
+$468万
+$18,712/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$751万
+$23,335/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$812万
+$19,623/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$761万
-$23,630/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$823万
-$19,872/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -37685,13 +38009,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -37699,71 +38023,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-招标单位
--
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$953万
+$20,987/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$618万
+$18,781/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$711万
+$22,859/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$626万
-$19,015/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$720万
-$23,145/呎
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$579万
+$18,106/呎
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$576万
+$17,991/呎
+(26年-02月-25日)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$467万
+$18,668/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$750万
+$23,280/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$613万
-$19,156/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$583万
-$18,219/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$473万
-$18,904/呎
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$810万
+$19,575/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$676万
-$20,981/呎
-(26年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$820万
-$19,819/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -37772,13 +38096,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -37786,71 +38110,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$962万
-$21,198/呎
+$961万
+$21,172/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$616万
+$18,733/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$624万
-$18,967/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$718万
-$23,087/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
+$709万
+$22,801/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$611万
-$19,106/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
+$604万
+$18,872/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$582万
-$18,172/呎
-(26年-02月-23日)</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
+$574万
+$17,944/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
 $471万
-$18,852/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
+$18,828/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$757万
-$23,512/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
+$666万
+$20,668/呎
+(26年-10月-17日)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$818万
-$19,771/呎
+$817万
+$19,744/呎
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -37859,13 +38183,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -37873,71 +38197,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-$755万
-$22,867/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 454呎 (2房)
+$959万
+$21,117/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$615万
+$18,687/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$716万
-$23,029/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-$735万
-$23,028/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-$738万
-$23,144/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>G | 249呎 (开放式)
-$572万
-$22,952/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
+$630万
+$20,241/呎
+(26年-10月-13日)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$602万
+$18,825/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$573万
+$17,900/呎
+(26年-02月-05日)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$475万
+$18,992/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$755万
-$23,453/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
+$664万
+$20,615/呎
+(26年-10月-17日)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="22" t="inlineStr">
+$815万
+$19,696/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -37946,13 +38270,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -37960,71 +38284,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$955万
-$21,040/呎
+$946万
+$20,830/呎
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$619万
-$18,827/呎
+$613万
+$18,641/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$713万
-$22,913/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
+$706万
+$22,688/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$607万
-$18,966/呎
+$601万
+$18,775/呎
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$577万
-$18,038/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
+$571万
+$17,856/呎
+(26年-02月-02日)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
 $468万
-$18,712/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+$18,736/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$751万
-$23,335/呎
+$744万
+$23,106/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$812万
-$19,623/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr">
+$804万
+$19,428/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38033,13 +38357,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38047,71 +38371,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$953万
-$20,987/呎
+$943万
+$20,780/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$612万
+$18,593/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$704万
+$22,630/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$599万
+$18,728/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$570万
+$17,812/呎
+(26年-01月-23日)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$462万
+$18,480/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$660万
+$20,512/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$811万
+$19,599/呎
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$618万
-$18,781/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$711万
-$22,859/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$579万
-$18,106/呎
-(26年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$576万
-$17,991/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$467万
-$18,668/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$750万
-$23,280/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$810万
-$19,575/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38120,13 +38444,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38134,71 +38458,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$961万
-$21,172/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
+$923万
+$20,322/呎
+(26年-03月-03日)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$616万
-$18,733/呎
+$610万
+$18,547/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$709万
-$22,801/呎
+$702万
+$22,576/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$604万
-$18,872/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
+$566万
+$17,678/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$574万
-$17,944/呎
-(26年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
+$568万
+$17,766/呎
+(26年-02月-04日)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$471万
-$18,828/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
+$461万
+$18,436/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$748万
-$23,220/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
+$659万
+$20,463/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$817万
-$19,744/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
+$800万
+$19,331/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38207,13 +38531,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38221,71 +38545,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$959万
-$21,117/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
+$931万
+$20,500/呎
+(26年-03月-05日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$615万
-$18,687/呎
+$609万
+$18,498/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$630万
-$20,241/呎
-(26年-10月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
+$700万
+$22,518/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$602万
-$18,825/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
+$564万
+$17,634/呎
+(26年-01月-08日)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$573万
-$17,900/呎
-(26年-02月-05日)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
+$567万
+$17,722/呎
+(26年-02月-06日)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$475万
-$18,992/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
+$465万
+$18,596/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$746万
-$23,161/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
+$657万
+$20,410/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$815万
-$19,696/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
+$798万
+$19,285/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38294,13 +38618,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38308,71 +38632,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$946万
-$20,830/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
+$918万
+$20,220/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$613万
-$18,641/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
+$607万
+$18,453/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$706万
-$22,688/呎
+$699万
+$22,463/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$601万
-$18,775/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
+$563万
+$17,591/呎
+(26年-01月-13日)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$571万
-$17,856/呎
-(26年-02月-02日)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
+$566万
+$17,678/呎
+(26年-02月-06日)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$468万
-$18,736/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
+$459万
+$18,344/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$744万
-$23,106/呎
+$737万
+$22,876/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$804万
-$19,428/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="K20" s="22" t="inlineStr">
+$796万
+$19,234/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38381,13 +38705,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38395,71 +38719,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$943万
-$20,780/呎
+$913万
+$20,119/呎
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 329呎 (1房)
+$604万
+$18,362/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 311呎 (1房)
+$619万
+$19,894/呎
+(26年-10月-26日)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 320呎 (1房)
+$560万
+$17,503/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$563万
+$17,591/呎
+(26年-02月-16日)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$426万
+$17,056/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>H | 322呎 (1房)
+$733万
+$22,761/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 414呎 (2房)
+$792万
+$19,140/呎
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$612万
-$18,593/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$704万
-$22,630/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$599万
-$18,728/呎
-(26年-05月-04日)</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$570万
-$17,812/呎
-(26年-01月-23日)</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$462万
-$18,480/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$660万
-$20,512/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$811万
-$19,599/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38468,13 +38792,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38482,71 +38806,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$923万
-$20,322/呎
-(26年-03月-03日)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
+$911万
+$20,068/呎
+(26年-02月-11日)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$610万
-$18,547/呎
+$603万
+$18,319/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$702万
-$22,576/呎
+$693万
+$22,293/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$566万
-$17,678/呎
-(26年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
+$559万
+$17,462/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$568万
-$17,766/呎
-(26年-02月-04日)</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
+$562万
+$17,547/呎
+(26年-02月-06日)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$461万
-$18,436/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="I22" s="23" t="inlineStr">
+$425万
+$17,016/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$740万
-$22,991/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
+$651万
+$20,208/呎
+(26年-10月-26日)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$800万
-$19,331/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
+$790万
+$19,094/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38555,13 +38879,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38569,71 +38893,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$931万
-$20,500/呎
-(26年-03月-05日)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
+$909万
+$20,018/呎
+(26年-02月-05日)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$609万
-$18,498/呎
+$601万
+$18,274/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$700万
-$22,518/呎
+$692万
+$22,238/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$564万
-$17,634/呎
-(26年-01月-08日)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
+$557万
+$17,419/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$567万
-$17,722/呎
-(26年-02月-06日)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
+$560万
+$17,503/呎
+(26年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$465万
-$18,596/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
+$424万
+$16,972/呎
+(26年-01月-14日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$657万
-$20,410/呎
-(26年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
+$649万
+$20,158/呎
+(26年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$798万
-$19,285/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="K23" s="22" t="inlineStr">
+$744万
+$17,966/呎
+(26年-01月-14日)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38642,13 +38966,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38656,71 +38980,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$918万
-$20,220/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
+$906万
+$19,967/呎
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$607万
-$18,453/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
+$606万
+$18,432/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$699万
-$22,463/呎
+$690万
+$22,183/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$563万
-$17,591/呎
-(26年-01月-13日)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
+$556万
+$17,372/呎
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$566万
-$17,678/呎
-(26年-02月-06日)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
+$559万
+$17,459/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$459万
-$18,344/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
+$442万
+$17,700/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$737万
-$22,876/呎
+$728万
+$22,593/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J24" s="20" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$796万
-$19,234/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
+$776万
+$18,737/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38729,13 +39053,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38743,71 +39067,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$913万
-$20,119/呎
+$904万
+$19,919/呎
 (26年-03月-02日)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$604万
-$18,362/呎
+$598万
+$18,179/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$619万
-$19,894/呎
-(26年-10月-04日)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
+$688万
+$22,129/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$560万
-$17,503/呎
+$554万
+$17,328/呎
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$563万
-$17,591/呎
-(26年-02月-16日)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
+$557万
+$17,419/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$426万
-$17,056/呎
+$422万
+$16,888/呎
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="I29" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$733万
-$22,761/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
+$726万
+$22,534/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$792万
-$19,140/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
+$774万
+$18,691/呎
+(26年-01月-09日)</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38816,13 +39140,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38830,71 +39154,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$911万
-$20,068/呎
-(26年-02月-11日)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
+$902万
+$19,868/呎
+(26年-01月-14日)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$603万
-$18,319/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
+$597万
+$18,134/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$693万
-$22,293/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
+$618万
+$19,868/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$559万
-$17,462/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
+$553万
+$17,284/呎
+(26年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$562万
-$17,547/呎
-(26年-02月-06日)</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
+$556万
+$17,372/呎
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$425万
-$17,016/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="I26" s="23" t="inlineStr">
+$421万
+$16,844/呎
+(26年-01月-08日)</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$731万
-$22,705/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr">
+$724万
+$22,478/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$790万
-$19,094/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="K26" s="22" t="inlineStr">
+$738万
+$17,833/呎
+(26年-01月-07日)</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38903,13 +39227,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -38917,71 +39241,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$909万
-$20,018/呎
-(26年-02月-05日)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
+$900万
+$19,819/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$601万
-$18,274/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+$595万
+$18,091/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$692万
-$22,238/呎
+$685万
+$22,016/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$557万
-$17,419/呎
+$577万
+$18,028/呎
+(26年-01月-13日)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 320呎 (1房)
+$561万
+$17,525/呎
+(26年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 250呎 (开放式)
+$420万
+$16,804/呎
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$560万
-$17,503/呎
-(26年-01月-26日)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$424万
-$16,972/呎
-(26年-01月-14日)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="I31" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$649万
-$20,158/呎
-(26年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="inlineStr">
+$722万
+$22,422/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$744万
-$17,966/呎
-(26年-01月-14日)</t>
-        </is>
-      </c>
-      <c r="K27" s="22" t="inlineStr">
+$736万
+$17,787/呎
+(25年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -38990,13 +39314,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -39004,71 +39328,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$906万
-$19,967/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
+$908万
+$19,996/呎
+(26年-03月-16日)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$606万
-$18,432/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
+$594万
+$18,046/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$690万
-$22,183/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
+$683万
+$21,961/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$556万
-$17,372/呎
-(26年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
+$582万
+$18,178/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$559万
-$17,459/呎
-(26年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
+$553万
+$17,284/呎
+(26年-02月-11日)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$442万
-$17,700/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="I28" s="24" t="inlineStr">
+$419万
+$16,764/呎
+(26年-01月-14日)</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$728万
-$22,593/呎
+$720万
+$22,366/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$776万
-$18,737/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="K28" s="22" t="inlineStr">
+$735万
+$17,744/呎
+(26年-01月-07日)</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -39077,13 +39401,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -39091,71 +39415,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$904万
-$19,919/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
+$903万
+$19,894/呎
+(26年-03月-17日)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$598万
-$18,179/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+$596万
+$18,106/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$688万
-$22,129/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$554万
-$17,328/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="inlineStr">
+$680万
+$21,852/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+$622万
+$19,508/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
-$557万
-$17,419/呎
-(26年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
+$548万
+$17,116/呎
+(26年-02月-25日)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$422万
-$16,888/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="I29" s="24" t="inlineStr">
+$451万
+$18,044/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$726万
-$22,534/呎
+$717万
+$22,255/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J29" s="20" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$774万
-$18,691/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="K29" s="22" t="inlineStr">
+$731万
+$17,657/呎
+(26年-01月-08日)</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -39164,13 +39488,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -39178,71 +39502,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 454呎 (2房)
-$902万
-$19,868/呎
-(26年-01月-14日)</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
+$919万
+$20,240/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 329呎 (1房)
-$597万
-$18,134/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
+$594万
+$18,061/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$618万
-$19,868/呎
-(26年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="F30" s="20" t="inlineStr">
+$603万
+$19,402/呎
+(26年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
-$553万
-$17,284/呎
-(26年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$556万
-$17,372/呎
-(26年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr">
+$546万
+$17,075/呎
+(26年-01月-15日)</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+$621万
+$19,458/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$421万
-$16,844/呎
-(26年-01月-08日)</t>
-        </is>
-      </c>
-      <c r="I30" s="24" t="inlineStr">
+$450万
+$18,000/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$724万
-$22,478/呎
+$715万
+$22,202/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J30" s="20" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$738万
-$17,833/呎
-(26年-01月-07日)</t>
-        </is>
-      </c>
-      <c r="K30" s="22" t="inlineStr">
+$782万
+$18,877/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -39251,13 +39575,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -39265,71 +39589,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$900万
-$19,819/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$595万
-$18,091/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 455呎 (2房)
+$1008万
+$22,158/呎
+(26年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+$712万
+$21,591/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$685万
-$22,016/呎
+$676万
+$21,746/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+$694万
+$21,743/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$577万
-$18,028/呎
-(26年-01月-13日)</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$561万
-$17,525/呎
-(26年-01月-26日)</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+$694万
+$21,743/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$420万
-$16,804/呎
-(26年-01月-09日)</t>
-        </is>
-      </c>
-      <c r="I31" s="24" t="inlineStr">
+$480万
+$19,216/呎
+(26年-10月-13日)</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$722万
-$22,422/呎
+$713万
+$22,146/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J31" s="20" t="inlineStr">
+      <c r="J35" s="23" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$736万
-$17,787/呎
-(25年-12月-14日)</t>
-        </is>
-      </c>
-      <c r="K31" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -39338,13 +39662,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 468呎 (2房)
 -
@@ -39352,71 +39676,71 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$908万
-$19,996/呎
-(26年-03月-16日)</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$594万
-$18,046/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$823万
+$24,215/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>C | 330呎 (1房)
+$700万
+$21,215/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
-$683万
-$21,961/呎
+$664万
+$21,363/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>E | 319呎 (1房)
+$682万
+$21,364/呎
 (在售)</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$582万
-$18,178/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$553万
-$17,284/呎
-(26年-02月-11日)</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>F | 319呎 (1房)
+$682万
+$21,364/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>G | 250呎 (开放式)
-$419万
-$16,764/呎
-(26年-01月-14日)</t>
-        </is>
-      </c>
-      <c r="I32" s="24" t="inlineStr">
+$472万
+$18,876/呎
+(26年-10月-16日)</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
-$720万
-$22,366/呎
+$711万
+$22,090/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J32" s="20" t="inlineStr">
+      <c r="J36" s="23" t="inlineStr">
         <is>
           <t>J | 414呎 (2房)
-$735万
-$17,744/呎
-(26年-01月-07日)</t>
-        </is>
-      </c>
-      <c r="K32" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
         <is>
           <t>K | 423呎 (2房)
 -
@@ -39425,354 +39749,6 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$903万
-$19,894/呎
-(26年-03月-17日)</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$596万
-$18,106/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$680万
-$21,852/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-$622万
-$19,508/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr">
-        <is>
-          <t>F | 320呎 (1房)
-$548万
-$17,116/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$451万
-$18,044/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="I33" s="24" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$717万
-$22,255/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J33" s="20" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$731万
-$17,657/呎
-(26年-01月-08日)</t>
-        </is>
-      </c>
-      <c r="K33" s="22" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>B | 454呎 (2房)
-$919万
-$20,240/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>C | 329呎 (1房)
-$594万
-$18,061/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$603万
-$19,402/呎
-(26年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>E | 320呎 (1房)
-$546万
-$17,075/呎
-(26年-01月-15日)</t>
-        </is>
-      </c>
-      <c r="G34" s="25" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-$621万
-$19,458/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$450万
-$18,000/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="I34" s="24" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$715万
-$22,202/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-$782万
-$18,877/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="K34" s="22" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>B | 455呎 (2房)
-$1008万
-$22,158/呎
-(26年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-$712万
-$21,591/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$676万
-$21,746/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-$694万
-$21,743/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-$694万
-$21,743/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$480万
-$19,216/呎
-(26年-10月-13日)</t>
-        </is>
-      </c>
-      <c r="I35" s="24" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$713万
-$22,146/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="K35" s="22" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>A | 468呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$823万
-$24,215/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>C | 330呎 (1房)
-$700万
-$21,215/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>D | 311呎 (1房)
-$664万
-$21,363/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>E | 319呎 (1房)
-$682万
-$21,364/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>F | 319呎 (1房)
-$682万
-$21,364/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>G | 250呎 (开放式)
-$472万
-$18,876/呎
-(26年-10月-16日)</t>
-        </is>
-      </c>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>H | 322呎 (1房)
-$711万
-$22,090/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>J | 414呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="K36" s="22" t="inlineStr">
-        <is>
-          <t>K | 423呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="19" t="inlineStr">
         <is>
@@ -39803,12 +39779,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>D | 311呎 (1房)
 $650万
 $20,884/呎
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">

--- a/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
+++ b/九龙-启德-Double Coast III/Double Coast III_销控明细表.xlsx
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>46682000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>33877</v>
+        <v>34000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>46682000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>33877</v>
+        <v>34000</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>18120000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>26072</v>
+        <v>26034</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>18120000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>26072</v>
+        <v>26034</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>8748000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>20297</v>
+        <v>20344</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>8748000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>20297</v>
+        <v>20344</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>7907000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>18346</v>
+        <v>18388</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>7907000</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>18346</v>
+        <v>18388</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>7888000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>18302</v>
+        <v>18344</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>7888000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>18302</v>
+        <v>18344</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>16312000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>23471</v>
+        <v>23437</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>16312000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>23471</v>
+        <v>23437</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>7956000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>18459</v>
+        <v>18502</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>7956000</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>18459</v>
+        <v>18502</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>16059000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>25092</v>
+        <v>25053</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>16059000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>25092</v>
+        <v>25053</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>7897000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>18323</v>
+        <v>18365</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>7897000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>18323</v>
+        <v>18365</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>7877000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>18276</v>
+        <v>18319</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         <v>7877000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>18276</v>
+        <v>18319</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>15579000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>22416</v>
+        <v>22384</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>15579000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>22416</v>
+        <v>22384</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>7857000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>18230</v>
+        <v>18272</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>7857000</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>18230</v>
+        <v>18272</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>7925000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>18387</v>
+        <v>18430</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>7925000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>18387</v>
+        <v>18430</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>15501000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>22304</v>
+        <v>22272</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>15501000</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>22304</v>
+        <v>22272</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>7818000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>18139</v>
+        <v>18181</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>7818000</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>18139</v>
+        <v>18181</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>15463000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>22249</v>
+        <v>22217</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>15463000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>22249</v>
+        <v>22217</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>7799000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>18095</v>
+        <v>18137</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>7799000</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>18095</v>
+        <v>18137</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>15424000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>22193</v>
+        <v>22161</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>15424000</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>22193</v>
+        <v>22161</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>14441000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>22564</v>
+        <v>22529</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>14441000</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>22564</v>
+        <v>22529</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>7693000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>17849</v>
+        <v>17891</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>7693000</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>17849</v>
+        <v>17891</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>15560000</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>22388</v>
+        <v>22356</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>15560000</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>22388</v>
+        <v>22356</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>14325000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>22383</v>
+        <v>22348</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>14325000</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>22383</v>
+        <v>22348</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>7760000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>18005</v>
+        <v>18047</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>7760000</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>18005</v>
+        <v>18047</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>16044000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>23085</v>
+        <v>23052</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>16044000</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>23085</v>
+        <v>23052</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>14289000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>22327</v>
+        <v>22292</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>14289000</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>22327</v>
+        <v>22292</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>7290000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>16914</v>
+        <v>16953</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>7290000</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>16914</v>
+        <v>16953</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>15309000</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>22027</v>
+        <v>21996</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>15309000</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>22027</v>
+        <v>21996</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>14334000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>22397</v>
+        <v>22362</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>14334000</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>22397</v>
+        <v>22362</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>7253000</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>16828</v>
+        <v>16867</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>7253000</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>16828</v>
+        <v>16867</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>15232000</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>21917</v>
+        <v>21885</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>15232000</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>21917</v>
+        <v>21885</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>14262000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>22284</v>
+        <v>22250</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>14262000</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>22284</v>
+        <v>22250</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>7236000</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>16789</v>
+        <v>16828</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>7236000</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>16789</v>
+        <v>16828</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>15195000</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>21863</v>
+        <v>21832</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>15195000</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>21863</v>
+        <v>21832</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>14147000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>22105</v>
+        <v>22070</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>14147000</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>22105</v>
+        <v>22070</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>7217000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>16745</v>
+        <v>16784</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>7217000</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>16745</v>
+        <v>16784</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>15157000</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>21809</v>
+        <v>21777</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>15157000</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>21809</v>
+        <v>21777</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>13569000</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>21202</v>
+        <v>21168</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>13569000</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>21202</v>
+        <v>21168</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>7200000</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>16705</v>
+        <v>16744</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>7200000</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>16705</v>
+        <v>16744</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>15119000</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>21754</v>
+        <v>21723</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>15119000</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>21754</v>
+        <v>21723</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>14156000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>22119</v>
+        <v>22084</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>14156000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>22119</v>
+        <v>22084</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>7181000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>16661</v>
+        <v>16700</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>7181000</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>16661</v>
+        <v>16700</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>15081000</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>21699</v>
+        <v>21668</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>15081000</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>21699</v>
+        <v>21668</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>14042000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>21941</v>
+        <v>21906</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>14042000</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>21941</v>
+        <v>21906</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>7164000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>16622</v>
+        <v>16660</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>7164000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>16622</v>
+        <v>16660</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>15215000</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>21892</v>
+        <v>21861</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>15215000</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>21892</v>
+        <v>21861</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>14006000</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>21884</v>
+        <v>21850</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>14006000</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>21884</v>
+        <v>21850</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>7503000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>17408</v>
+        <v>17449</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>7503000</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>17408</v>
+        <v>17449</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>15006000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>21591</v>
+        <v>21560</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>15006000</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>21591</v>
+        <v>21560</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>13972000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>21831</v>
+        <v>21797</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>13972000</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>21831</v>
+        <v>21797</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>7485000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>17367</v>
+        <v>17407</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>7485000</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>17367</v>
+        <v>17407</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>14969000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>21538</v>
+        <v>21507</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>14969000</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>21538</v>
+        <v>21507</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>13401000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>20939</v>
+        <v>20906</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>13401000</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>20939</v>
+        <v>20906</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>7531000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>17473</v>
+        <v>17514</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>7531000</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>17473</v>
+        <v>17514</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>15571000</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>22404</v>
+        <v>22372</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>15571000</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>22404</v>
+        <v>22372</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>7428000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>17234</v>
+        <v>17274</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>7428000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>17234</v>
+        <v>17274</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12923,38 +12923,30 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>16894000</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>24273</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L186" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K186" s="5" t="n">
+        <v>16894000</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>24273</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12963,7 +12955,7 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14622,7 +14614,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -15274,7 +15266,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15917,7 +15909,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -15933,7 +15925,7 @@
         <v>4784000</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>19136</v>
+        <v>19213</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -15944,7 +15936,7 @@
         <v>4784000</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>19136</v>
+        <v>19213</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -15979,7 +15971,7 @@
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
@@ -15995,7 +15987,7 @@
         <v>6198000</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>19369</v>
+        <v>19429</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -16006,7 +15998,7 @@
         <v>6198000</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>19369</v>
+        <v>19429</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
@@ -16041,7 +16033,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -16057,7 +16049,7 @@
         <v>6218000</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>19431</v>
+        <v>19492</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16068,7 +16060,7 @@
         <v>6218000</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>19431</v>
+        <v>19492</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -16165,7 +16157,7 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
@@ -16181,7 +16173,7 @@
         <v>6388000</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>19416</v>
+        <v>19358</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -16192,7 +16184,7 @@
         <v>6388000</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>19416</v>
+        <v>19358</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -16561,7 +16553,7 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -16577,7 +16569,7 @@
         <v>4773000</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>19092</v>
+        <v>19169</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -16588,7 +16580,7 @@
         <v>4773000</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>19092</v>
+        <v>19169</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
@@ -16623,7 +16615,7 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -16639,7 +16631,7 @@
         <v>6182000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>19319</v>
+        <v>19379</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -16650,7 +16642,7 @@
         <v>6182000</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>19319</v>
+        <v>19379</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -16685,7 +16677,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -16701,7 +16693,7 @@
         <v>6203000</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>19384</v>
+        <v>19445</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -16712,7 +16704,7 @@
         <v>6203000</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>19384</v>
+        <v>19445</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -16809,7 +16801,7 @@
         </is>
       </c>
       <c r="E245" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
@@ -16825,7 +16817,7 @@
         <v>6372000</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>19368</v>
+        <v>19309</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -16836,7 +16828,7 @@
         <v>6372000</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>19368</v>
+        <v>19309</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -17205,7 +17197,7 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -17221,7 +17213,7 @@
         <v>4815000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>19260</v>
+        <v>19337</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -17232,7 +17224,7 @@
         <v>4815000</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>19260</v>
+        <v>19337</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -17267,7 +17259,7 @@
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
@@ -17283,7 +17275,7 @@
         <v>6218000</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>19431</v>
+        <v>19492</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
@@ -17294,7 +17286,7 @@
         <v>6218000</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>19431</v>
+        <v>19492</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
@@ -17329,7 +17321,7 @@
         </is>
       </c>
       <c r="E253" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
@@ -17345,7 +17337,7 @@
         <v>6188000</v>
       </c>
       <c r="I253" s="5" t="n">
-        <v>19338</v>
+        <v>19398</v>
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
@@ -17356,7 +17348,7 @@
         <v>6188000</v>
       </c>
       <c r="L253" s="5" t="n">
-        <v>19338</v>
+        <v>19398</v>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
@@ -17453,7 +17445,7 @@
         </is>
       </c>
       <c r="E255" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
@@ -17469,7 +17461,7 @@
         <v>6427000</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>19535</v>
+        <v>19476</v>
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
@@ -17480,7 +17472,7 @@
         <v>6427000</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>19535</v>
+        <v>19476</v>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
@@ -17849,7 +17841,7 @@
         </is>
       </c>
       <c r="E261" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
@@ -17865,7 +17857,7 @@
         <v>4749000</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>18996</v>
+        <v>19072</v>
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
@@ -17876,7 +17868,7 @@
         <v>4749000</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>18996</v>
+        <v>19072</v>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
@@ -17911,7 +17903,7 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -17927,7 +17919,7 @@
         <v>6220000</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>19438</v>
+        <v>19498</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
@@ -17938,7 +17930,7 @@
         <v>6220000</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>19438</v>
+        <v>19498</v>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
@@ -17973,7 +17965,7 @@
         </is>
       </c>
       <c r="E263" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
@@ -17989,7 +17981,7 @@
         <v>6173000</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>19291</v>
+        <v>19351</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
@@ -18000,7 +17992,7 @@
         <v>6173000</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>19291</v>
+        <v>19351</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -18097,7 +18089,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -18113,7 +18105,7 @@
         <v>6287000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>19109</v>
+        <v>19052</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -18124,7 +18116,7 @@
         <v>6287000</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>19109</v>
+        <v>19052</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -18435,7 +18427,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -18462,7 +18454,7 @@
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
@@ -18493,7 +18485,7 @@
         </is>
       </c>
       <c r="E271" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
@@ -18509,7 +18501,7 @@
         <v>4737000</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>18948</v>
+        <v>19024</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
@@ -18520,7 +18512,7 @@
         <v>4737000</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>18948</v>
+        <v>19024</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
@@ -18555,7 +18547,7 @@
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
@@ -18571,7 +18563,7 @@
         <v>6136000</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>19175</v>
+        <v>19235</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -18582,7 +18574,7 @@
         <v>6136000</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>19175</v>
+        <v>19235</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
@@ -18617,7 +18609,7 @@
         </is>
       </c>
       <c r="E273" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
@@ -18633,7 +18625,7 @@
         <v>6157000</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>19241</v>
+        <v>19301</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
@@ -18644,7 +18636,7 @@
         <v>6157000</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>19241</v>
+        <v>19301</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
@@ -18741,7 +18733,7 @@
         </is>
       </c>
       <c r="E275" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
@@ -18757,7 +18749,7 @@
         <v>6271000</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>19061</v>
+        <v>19003</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
@@ -18768,7 +18760,7 @@
         <v>6271000</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>19061</v>
+        <v>19003</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -19084,7 +19076,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19137,7 +19129,7 @@
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
@@ -19153,7 +19145,7 @@
         <v>4726000</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>18904</v>
+        <v>18980</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
@@ -19164,7 +19156,7 @@
         <v>4726000</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>18904</v>
+        <v>18980</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
@@ -19199,7 +19191,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -19215,7 +19207,7 @@
         <v>5830000</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>18219</v>
+        <v>18276</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -19226,7 +19218,7 @@
         <v>5830000</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>18219</v>
+        <v>18276</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
@@ -19261,7 +19253,7 @@
         </is>
       </c>
       <c r="E283" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
@@ -19277,7 +19269,7 @@
         <v>6130000</v>
       </c>
       <c r="I283" s="5" t="n">
-        <v>19156</v>
+        <v>19216</v>
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
@@ -19288,7 +19280,7 @@
         <v>6130000</v>
       </c>
       <c r="L283" s="5" t="n">
-        <v>19156</v>
+        <v>19216</v>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
@@ -19385,7 +19377,7 @@
         </is>
       </c>
       <c r="E285" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
@@ -19401,7 +19393,7 @@
         <v>6256000</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>19015</v>
+        <v>18958</v>
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
@@ -19412,7 +19404,7 @@
         <v>6256000</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>19015</v>
+        <v>18958</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
@@ -19773,7 +19765,7 @@
         </is>
       </c>
       <c r="E291" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
@@ -19789,7 +19781,7 @@
         <v>4713000</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>18852</v>
+        <v>18928</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
@@ -19800,7 +19792,7 @@
         <v>4713000</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>18852</v>
+        <v>18928</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -19835,7 +19827,7 @@
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
@@ -19851,7 +19843,7 @@
         <v>5815000</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>18172</v>
+        <v>18229</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -19862,7 +19854,7 @@
         <v>5815000</v>
       </c>
       <c r="L292" s="5" t="n">
-        <v>18172</v>
+        <v>18229</v>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
@@ -19897,7 +19889,7 @@
         </is>
       </c>
       <c r="E293" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
@@ -19913,7 +19905,7 @@
         <v>6114000</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>19106</v>
+        <v>19166</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
@@ -19924,7 +19916,7 @@
         <v>6114000</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>19106</v>
+        <v>19166</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
@@ -20021,7 +20013,7 @@
         </is>
       </c>
       <c r="E295" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
@@ -20037,7 +20029,7 @@
         <v>6240000</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>18967</v>
+        <v>18909</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
@@ -20048,7 +20040,7 @@
         <v>6240000</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>18967</v>
+        <v>18909</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
@@ -20083,7 +20075,7 @@
         </is>
       </c>
       <c r="E296" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
@@ -20099,7 +20091,7 @@
         <v>9624000</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>21198</v>
+        <v>21152</v>
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
@@ -20110,7 +20102,7 @@
         <v>9624000</v>
       </c>
       <c r="L296" s="5" t="n">
-        <v>21198</v>
+        <v>21152</v>
       </c>
       <c r="M296" s="3" t="inlineStr">
         <is>
@@ -21003,7 +20995,7 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -21030,7 +21022,7 @@
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N310" s="3" t="inlineStr">
@@ -21061,7 +21053,7 @@
         </is>
       </c>
       <c r="E311" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
@@ -21077,7 +21069,7 @@
         <v>4678000</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>18712</v>
+        <v>18787</v>
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
@@ -21088,7 +21080,7 @@
         <v>4678000</v>
       </c>
       <c r="L311" s="5" t="n">
-        <v>18712</v>
+        <v>18787</v>
       </c>
       <c r="M311" s="3" t="inlineStr">
         <is>
@@ -21123,7 +21115,7 @@
         </is>
       </c>
       <c r="E312" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
@@ -21139,7 +21131,7 @@
         <v>5772000</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>18038</v>
+        <v>18094</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
@@ -21150,7 +21142,7 @@
         <v>5772000</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>18038</v>
+        <v>18094</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
@@ -21185,7 +21177,7 @@
         </is>
       </c>
       <c r="E313" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
@@ -21201,7 +21193,7 @@
         <v>6069000</v>
       </c>
       <c r="I313" s="5" t="n">
-        <v>18966</v>
+        <v>19025</v>
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
@@ -21212,7 +21204,7 @@
         <v>6069000</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>18966</v>
+        <v>19025</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
@@ -21309,7 +21301,7 @@
         </is>
       </c>
       <c r="E315" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
@@ -21325,7 +21317,7 @@
         <v>6194000</v>
       </c>
       <c r="I315" s="5" t="n">
-        <v>18827</v>
+        <v>18770</v>
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
@@ -21336,7 +21328,7 @@
         <v>6194000</v>
       </c>
       <c r="L315" s="5" t="n">
-        <v>18827</v>
+        <v>18770</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
@@ -21371,7 +21363,7 @@
         </is>
       </c>
       <c r="E316" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
@@ -21387,7 +21379,7 @@
         <v>9552000</v>
       </c>
       <c r="I316" s="5" t="n">
-        <v>21040</v>
+        <v>20993</v>
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
@@ -21398,7 +21390,7 @@
         <v>9552000</v>
       </c>
       <c r="L316" s="5" t="n">
-        <v>21040</v>
+        <v>20993</v>
       </c>
       <c r="M316" s="3" t="inlineStr">
         <is>
@@ -21639,7 +21631,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -21666,7 +21658,7 @@
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N320" s="3" t="inlineStr">
@@ -21697,7 +21689,7 @@
         </is>
       </c>
       <c r="E321" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
@@ -21713,7 +21705,7 @@
         <v>4667000</v>
       </c>
       <c r="I321" s="5" t="n">
-        <v>18668</v>
+        <v>18743</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
@@ -21724,7 +21716,7 @@
         <v>4667000</v>
       </c>
       <c r="L321" s="5" t="n">
-        <v>18668</v>
+        <v>18743</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
@@ -21759,7 +21751,7 @@
         </is>
       </c>
       <c r="E322" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
@@ -21775,7 +21767,7 @@
         <v>5757000</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>17991</v>
+        <v>18047</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
@@ -21786,7 +21778,7 @@
         <v>5757000</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>17991</v>
+        <v>18047</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -21821,7 +21813,7 @@
         </is>
       </c>
       <c r="E323" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
@@ -21837,7 +21829,7 @@
         <v>5794000</v>
       </c>
       <c r="I323" s="5" t="n">
-        <v>18106</v>
+        <v>18163</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
@@ -21848,7 +21840,7 @@
         <v>5794000</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>18106</v>
+        <v>18163</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -21914,7 +21906,7 @@
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N324" s="3" t="inlineStr">
@@ -21945,7 +21937,7 @@
         </is>
       </c>
       <c r="E325" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
@@ -21961,7 +21953,7 @@
         <v>6179000</v>
       </c>
       <c r="I325" s="5" t="n">
-        <v>18781</v>
+        <v>18724</v>
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
@@ -21972,7 +21964,7 @@
         <v>6179000</v>
       </c>
       <c r="L325" s="5" t="n">
-        <v>18781</v>
+        <v>18724</v>
       </c>
       <c r="M325" s="3" t="inlineStr">
         <is>
@@ -22007,7 +21999,7 @@
         </is>
       </c>
       <c r="E326" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
@@ -22023,7 +22015,7 @@
         <v>9528000</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>20987</v>
+        <v>20941</v>
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
@@ -22034,7 +22026,7 @@
         <v>9528000</v>
       </c>
       <c r="L326" s="5" t="n">
-        <v>20987</v>
+        <v>20941</v>
       </c>
       <c r="M326" s="3" t="inlineStr">
         <is>
@@ -22333,7 +22325,7 @@
         </is>
       </c>
       <c r="E331" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
@@ -22349,7 +22341,7 @@
         <v>4707000</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>18828</v>
+        <v>18904</v>
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
@@ -22360,7 +22352,7 @@
         <v>4707000</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>18828</v>
+        <v>18904</v>
       </c>
       <c r="M331" s="3" t="inlineStr">
         <is>
@@ -22395,7 +22387,7 @@
         </is>
       </c>
       <c r="E332" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
@@ -22411,7 +22403,7 @@
         <v>5742000</v>
       </c>
       <c r="I332" s="5" t="n">
-        <v>17944</v>
+        <v>18000</v>
       </c>
       <c r="J332" s="3" t="inlineStr">
         <is>
@@ -22422,7 +22414,7 @@
         <v>5742000</v>
       </c>
       <c r="L332" s="5" t="n">
-        <v>17944</v>
+        <v>18000</v>
       </c>
       <c r="M332" s="3" t="inlineStr">
         <is>
@@ -22457,7 +22449,7 @@
         </is>
       </c>
       <c r="E333" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
@@ -22473,7 +22465,7 @@
         <v>6039000</v>
       </c>
       <c r="I333" s="5" t="n">
-        <v>18872</v>
+        <v>18931</v>
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
@@ -22484,7 +22476,7 @@
         <v>6039000</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>18872</v>
+        <v>18931</v>
       </c>
       <c r="M333" s="3" t="inlineStr">
         <is>
@@ -22550,7 +22542,7 @@
       </c>
       <c r="M334" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N334" s="3" t="inlineStr">
@@ -22581,7 +22573,7 @@
         </is>
       </c>
       <c r="E335" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
@@ -22597,7 +22589,7 @@
         <v>6163000</v>
       </c>
       <c r="I335" s="5" t="n">
-        <v>18733</v>
+        <v>18676</v>
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
@@ -22608,7 +22600,7 @@
         <v>6163000</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>18733</v>
+        <v>18676</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
@@ -22643,7 +22635,7 @@
         </is>
       </c>
       <c r="E336" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
@@ -22659,7 +22651,7 @@
         <v>9612000</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>21172</v>
+        <v>21125</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
@@ -22670,7 +22662,7 @@
         <v>9612000</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>21172</v>
+        <v>21125</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
@@ -22969,7 +22961,7 @@
         </is>
       </c>
       <c r="E341" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
@@ -22985,7 +22977,7 @@
         <v>4748000</v>
       </c>
       <c r="I341" s="5" t="n">
-        <v>18992</v>
+        <v>19068</v>
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
@@ -22996,7 +22988,7 @@
         <v>4748000</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>18992</v>
+        <v>19068</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
@@ -23031,7 +23023,7 @@
         </is>
       </c>
       <c r="E342" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
@@ -23047,7 +23039,7 @@
         <v>5728000</v>
       </c>
       <c r="I342" s="5" t="n">
-        <v>17900</v>
+        <v>17956</v>
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
@@ -23058,7 +23050,7 @@
         <v>5728000</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>17900</v>
+        <v>17956</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
@@ -23093,7 +23085,7 @@
         </is>
       </c>
       <c r="E343" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
@@ -23109,7 +23101,7 @@
         <v>6024000</v>
       </c>
       <c r="I343" s="5" t="n">
-        <v>18825</v>
+        <v>18884</v>
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
@@ -23120,7 +23112,7 @@
         <v>6024000</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>18825</v>
+        <v>18884</v>
       </c>
       <c r="M343" s="3" t="inlineStr">
         <is>
@@ -23217,7 +23209,7 @@
         </is>
       </c>
       <c r="E345" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
@@ -23233,7 +23225,7 @@
         <v>6148000</v>
       </c>
       <c r="I345" s="5" t="n">
-        <v>18687</v>
+        <v>18630</v>
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
@@ -23244,7 +23236,7 @@
         <v>6148000</v>
       </c>
       <c r="L345" s="5" t="n">
-        <v>18687</v>
+        <v>18630</v>
       </c>
       <c r="M345" s="3" t="inlineStr">
         <is>
@@ -23279,7 +23271,7 @@
         </is>
       </c>
       <c r="E346" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
@@ -23295,7 +23287,7 @@
         <v>9587000</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>21117</v>
+        <v>21070</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
@@ -23306,7 +23298,7 @@
         <v>9587000</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>21117</v>
+        <v>21070</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
@@ -23547,7 +23539,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -23574,7 +23566,7 @@
       </c>
       <c r="M350" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N350" s="3" t="inlineStr">
@@ -23605,7 +23597,7 @@
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
@@ -23621,7 +23613,7 @@
         <v>4684000</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>18736</v>
+        <v>18811</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
@@ -23632,7 +23624,7 @@
         <v>4684000</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>18736</v>
+        <v>18811</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
@@ -23667,7 +23659,7 @@
         </is>
       </c>
       <c r="E352" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
@@ -23683,7 +23675,7 @@
         <v>5714000</v>
       </c>
       <c r="I352" s="5" t="n">
-        <v>17856</v>
+        <v>17912</v>
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
@@ -23694,7 +23686,7 @@
         <v>5714000</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>17856</v>
+        <v>17912</v>
       </c>
       <c r="M352" s="3" t="inlineStr">
         <is>
@@ -23729,7 +23721,7 @@
         </is>
       </c>
       <c r="E353" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
@@ -23745,7 +23737,7 @@
         <v>6008000</v>
       </c>
       <c r="I353" s="5" t="n">
-        <v>18775</v>
+        <v>18834</v>
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
@@ -23756,7 +23748,7 @@
         <v>6008000</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>18775</v>
+        <v>18834</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
@@ -23822,7 +23814,7 @@
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N354" s="3" t="inlineStr">
@@ -23853,7 +23845,7 @@
         </is>
       </c>
       <c r="E355" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
@@ -23869,7 +23861,7 @@
         <v>6133000</v>
       </c>
       <c r="I355" s="5" t="n">
-        <v>18641</v>
+        <v>18585</v>
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
@@ -23880,7 +23872,7 @@
         <v>6133000</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>18641</v>
+        <v>18585</v>
       </c>
       <c r="M355" s="3" t="inlineStr">
         <is>
@@ -23915,7 +23907,7 @@
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
@@ -23931,7 +23923,7 @@
         <v>9457000</v>
       </c>
       <c r="I356" s="5" t="n">
-        <v>20830</v>
+        <v>20785</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
@@ -23942,7 +23934,7 @@
         <v>9457000</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>20830</v>
+        <v>20785</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
@@ -24241,7 +24233,7 @@
         </is>
       </c>
       <c r="E361" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
@@ -24257,7 +24249,7 @@
         <v>4620000</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>18480</v>
+        <v>18554</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
@@ -24268,7 +24260,7 @@
         <v>4620000</v>
       </c>
       <c r="L361" s="5" t="n">
-        <v>18480</v>
+        <v>18554</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
@@ -24303,7 +24295,7 @@
         </is>
       </c>
       <c r="E362" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
@@ -24319,7 +24311,7 @@
         <v>5700000</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>17812</v>
+        <v>17868</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
@@ -24330,7 +24322,7 @@
         <v>5700000</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>17812</v>
+        <v>17868</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
@@ -24365,7 +24357,7 @@
         </is>
       </c>
       <c r="E363" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
@@ -24381,7 +24373,7 @@
         <v>5993000</v>
       </c>
       <c r="I363" s="5" t="n">
-        <v>18728</v>
+        <v>18787</v>
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
@@ -24392,7 +24384,7 @@
         <v>5993000</v>
       </c>
       <c r="L363" s="5" t="n">
-        <v>18728</v>
+        <v>18787</v>
       </c>
       <c r="M363" s="3" t="inlineStr">
         <is>
@@ -24458,7 +24450,7 @@
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N364" s="3" t="inlineStr">
@@ -24489,7 +24481,7 @@
         </is>
       </c>
       <c r="E365" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
@@ -24505,7 +24497,7 @@
         <v>6117000</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>18593</v>
+        <v>18536</v>
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
@@ -24516,7 +24508,7 @@
         <v>6117000</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>18593</v>
+        <v>18536</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
@@ -24551,7 +24543,7 @@
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
@@ -24567,7 +24559,7 @@
         <v>9434000</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>20780</v>
+        <v>20734</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
@@ -24578,7 +24570,7 @@
         <v>9434000</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>20780</v>
+        <v>20734</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
@@ -24877,7 +24869,7 @@
         </is>
       </c>
       <c r="E371" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
@@ -24893,7 +24885,7 @@
         <v>4609000</v>
       </c>
       <c r="I371" s="5" t="n">
-        <v>18436</v>
+        <v>18510</v>
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
@@ -24904,7 +24896,7 @@
         <v>4609000</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>18436</v>
+        <v>18510</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
@@ -24939,7 +24931,7 @@
         </is>
       </c>
       <c r="E372" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
@@ -24955,7 +24947,7 @@
         <v>5685000</v>
       </c>
       <c r="I372" s="5" t="n">
-        <v>17766</v>
+        <v>17821</v>
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
@@ -24966,7 +24958,7 @@
         <v>5685000</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>17766</v>
+        <v>17821</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
@@ -25001,7 +24993,7 @@
         </is>
       </c>
       <c r="E373" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
@@ -25017,7 +25009,7 @@
         <v>5657000</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>17678</v>
+        <v>17734</v>
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
@@ -25028,7 +25020,7 @@
         <v>5657000</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>17678</v>
+        <v>17734</v>
       </c>
       <c r="M373" s="3" t="inlineStr">
         <is>
@@ -25094,7 +25086,7 @@
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N374" s="3" t="inlineStr">
@@ -25125,7 +25117,7 @@
         </is>
       </c>
       <c r="E375" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
@@ -25141,7 +25133,7 @@
         <v>6102000</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>18547</v>
+        <v>18491</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
@@ -25152,7 +25144,7 @@
         <v>6102000</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>18547</v>
+        <v>18491</v>
       </c>
       <c r="M375" s="3" t="inlineStr">
         <is>
@@ -25187,7 +25179,7 @@
         </is>
       </c>
       <c r="E376" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
@@ -25203,7 +25195,7 @@
         <v>9226000</v>
       </c>
       <c r="I376" s="5" t="n">
-        <v>20322</v>
+        <v>20277</v>
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
@@ -25214,7 +25206,7 @@
         <v>9226000</v>
       </c>
       <c r="L376" s="5" t="n">
-        <v>20322</v>
+        <v>20277</v>
       </c>
       <c r="M376" s="3" t="inlineStr">
         <is>
@@ -25513,7 +25505,7 @@
         </is>
       </c>
       <c r="E381" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
@@ -25529,7 +25521,7 @@
         <v>4649000</v>
       </c>
       <c r="I381" s="5" t="n">
-        <v>18596</v>
+        <v>18671</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
@@ -25540,7 +25532,7 @@
         <v>4649000</v>
       </c>
       <c r="L381" s="5" t="n">
-        <v>18596</v>
+        <v>18671</v>
       </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
@@ -25575,7 +25567,7 @@
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
@@ -25591,7 +25583,7 @@
         <v>5671000</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>17722</v>
+        <v>17777</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
@@ -25602,7 +25594,7 @@
         <v>5671000</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>17722</v>
+        <v>17777</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -25637,7 +25629,7 @@
         </is>
       </c>
       <c r="E383" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
@@ -25653,7 +25645,7 @@
         <v>5643000</v>
       </c>
       <c r="I383" s="5" t="n">
-        <v>17634</v>
+        <v>17690</v>
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
@@ -25664,7 +25656,7 @@
         <v>5643000</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>17634</v>
+        <v>17690</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
@@ -25730,7 +25722,7 @@
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -25761,7 +25753,7 @@
         </is>
       </c>
       <c r="E385" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
@@ -25777,7 +25769,7 @@
         <v>6086000</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>18498</v>
+        <v>18442</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
@@ -25788,7 +25780,7 @@
         <v>6086000</v>
       </c>
       <c r="L385" s="5" t="n">
-        <v>18498</v>
+        <v>18442</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
@@ -25823,7 +25815,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -25839,7 +25831,7 @@
         <v>9307000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>20500</v>
+        <v>20455</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -25850,7 +25842,7 @@
         <v>9307000</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>20500</v>
+        <v>20455</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -26091,7 +26083,7 @@
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
@@ -26118,7 +26110,7 @@
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -26149,7 +26141,7 @@
         </is>
       </c>
       <c r="E391" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
@@ -26165,7 +26157,7 @@
         <v>4586000</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>18344</v>
+        <v>18418</v>
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
@@ -26176,7 +26168,7 @@
         <v>4586000</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>18344</v>
+        <v>18418</v>
       </c>
       <c r="M391" s="3" t="inlineStr">
         <is>
@@ -26211,7 +26203,7 @@
         </is>
       </c>
       <c r="E392" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
@@ -26227,7 +26219,7 @@
         <v>5657000</v>
       </c>
       <c r="I392" s="5" t="n">
-        <v>17678</v>
+        <v>17734</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
@@ -26238,7 +26230,7 @@
         <v>5657000</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>17678</v>
+        <v>17734</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -26273,7 +26265,7 @@
         </is>
       </c>
       <c r="E393" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
@@ -26289,7 +26281,7 @@
         <v>5629000</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>17591</v>
+        <v>17646</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -26300,7 +26292,7 @@
         <v>5629000</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>17591</v>
+        <v>17646</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
@@ -26366,7 +26358,7 @@
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -26397,7 +26389,7 @@
         </is>
       </c>
       <c r="E395" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
@@ -26413,7 +26405,7 @@
         <v>6071000</v>
       </c>
       <c r="I395" s="5" t="n">
-        <v>18453</v>
+        <v>18397</v>
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
@@ -26424,7 +26416,7 @@
         <v>6071000</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>18453</v>
+        <v>18397</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
@@ -26459,7 +26451,7 @@
         </is>
       </c>
       <c r="E396" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
@@ -26475,7 +26467,7 @@
         <v>9180000</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>20220</v>
+        <v>20176</v>
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
@@ -26486,7 +26478,7 @@
         <v>9180000</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>20220</v>
+        <v>20176</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
@@ -26785,7 +26777,7 @@
         </is>
       </c>
       <c r="E401" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
@@ -26801,7 +26793,7 @@
         <v>4264000</v>
       </c>
       <c r="I401" s="5" t="n">
-        <v>17056</v>
+        <v>17124</v>
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
@@ -26812,7 +26804,7 @@
         <v>4264000</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>17056</v>
+        <v>17124</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
@@ -26847,7 +26839,7 @@
         </is>
       </c>
       <c r="E402" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
@@ -26863,7 +26855,7 @@
         <v>5629000</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>17591</v>
+        <v>17646</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
@@ -26874,7 +26866,7 @@
         <v>5629000</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>17591</v>
+        <v>17646</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -26909,7 +26901,7 @@
         </is>
       </c>
       <c r="E403" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
@@ -26925,7 +26917,7 @@
         <v>5601000</v>
       </c>
       <c r="I403" s="5" t="n">
-        <v>17503</v>
+        <v>17558</v>
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
@@ -26936,7 +26928,7 @@
         <v>5601000</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>17503</v>
+        <v>17558</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
@@ -27033,7 +27025,7 @@
         </is>
       </c>
       <c r="E405" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
@@ -27049,7 +27041,7 @@
         <v>6041000</v>
       </c>
       <c r="I405" s="5" t="n">
-        <v>18362</v>
+        <v>18306</v>
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
@@ -27060,7 +27052,7 @@
         <v>6041000</v>
       </c>
       <c r="L405" s="5" t="n">
-        <v>18362</v>
+        <v>18306</v>
       </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
@@ -27095,7 +27087,7 @@
         </is>
       </c>
       <c r="E406" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
@@ -27111,7 +27103,7 @@
         <v>9134000</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>20119</v>
+        <v>20075</v>
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
@@ -27122,7 +27114,7 @@
         <v>9134000</v>
       </c>
       <c r="L406" s="5" t="n">
-        <v>20119</v>
+        <v>20075</v>
       </c>
       <c r="M406" s="3" t="inlineStr">
         <is>
@@ -27421,7 +27413,7 @@
         </is>
       </c>
       <c r="E411" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
@@ -27437,7 +27429,7 @@
         <v>4254000</v>
       </c>
       <c r="I411" s="5" t="n">
-        <v>17016</v>
+        <v>17084</v>
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
@@ -27448,7 +27440,7 @@
         <v>4254000</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>17016</v>
+        <v>17084</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
@@ -27483,7 +27475,7 @@
         </is>
       </c>
       <c r="E412" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
@@ -27499,7 +27491,7 @@
         <v>5615000</v>
       </c>
       <c r="I412" s="5" t="n">
-        <v>17547</v>
+        <v>17602</v>
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
@@ -27510,7 +27502,7 @@
         <v>5615000</v>
       </c>
       <c r="L412" s="5" t="n">
-        <v>17547</v>
+        <v>17602</v>
       </c>
       <c r="M412" s="3" t="inlineStr">
         <is>
@@ -27545,7 +27537,7 @@
         </is>
       </c>
       <c r="E413" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
@@ -27561,7 +27553,7 @@
         <v>5588000</v>
       </c>
       <c r="I413" s="5" t="n">
-        <v>17462</v>
+        <v>17517</v>
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
@@ -27572,7 +27564,7 @@
         <v>5588000</v>
       </c>
       <c r="L413" s="5" t="n">
-        <v>17462</v>
+        <v>17517</v>
       </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
@@ -27638,7 +27630,7 @@
       </c>
       <c r="M414" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N414" s="3" t="inlineStr">
@@ -27669,7 +27661,7 @@
         </is>
       </c>
       <c r="E415" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
@@ -27685,7 +27677,7 @@
         <v>6027000</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>18319</v>
+        <v>18264</v>
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
@@ -27696,7 +27688,7 @@
         <v>6027000</v>
       </c>
       <c r="L415" s="5" t="n">
-        <v>18319</v>
+        <v>18264</v>
       </c>
       <c r="M415" s="3" t="inlineStr">
         <is>
@@ -27731,7 +27723,7 @@
         </is>
       </c>
       <c r="E416" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
@@ -27747,7 +27739,7 @@
         <v>9111000</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>20068</v>
+        <v>20024</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
@@ -27758,7 +27750,7 @@
         <v>9111000</v>
       </c>
       <c r="L416" s="5" t="n">
-        <v>20068</v>
+        <v>20024</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -28057,7 +28049,7 @@
         </is>
       </c>
       <c r="E421" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
@@ -28073,7 +28065,7 @@
         <v>4243000</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>16972</v>
+        <v>17040</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
@@ -28084,7 +28076,7 @@
         <v>4243000</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>16972</v>
+        <v>17040</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -28119,7 +28111,7 @@
         </is>
       </c>
       <c r="E422" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
@@ -28135,7 +28127,7 @@
         <v>5601000</v>
       </c>
       <c r="I422" s="5" t="n">
-        <v>17503</v>
+        <v>17558</v>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
@@ -28146,7 +28138,7 @@
         <v>5601000</v>
       </c>
       <c r="L422" s="5" t="n">
-        <v>17503</v>
+        <v>17558</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
@@ -28181,7 +28173,7 @@
         </is>
       </c>
       <c r="E423" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
@@ -28197,7 +28189,7 @@
         <v>5574000</v>
       </c>
       <c r="I423" s="5" t="n">
-        <v>17419</v>
+        <v>17473</v>
       </c>
       <c r="J423" s="3" t="inlineStr">
         <is>
@@ -28208,7 +28200,7 @@
         <v>5574000</v>
       </c>
       <c r="L423" s="5" t="n">
-        <v>17419</v>
+        <v>17473</v>
       </c>
       <c r="M423" s="3" t="inlineStr">
         <is>
@@ -28274,7 +28266,7 @@
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N424" s="3" t="inlineStr">
@@ -28305,7 +28297,7 @@
         </is>
       </c>
       <c r="E425" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
@@ -28321,7 +28313,7 @@
         <v>6012000</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>18274</v>
+        <v>18218</v>
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
@@ -28332,7 +28324,7 @@
         <v>6012000</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>18274</v>
+        <v>18218</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -28367,7 +28359,7 @@
         </is>
       </c>
       <c r="E426" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
@@ -28383,7 +28375,7 @@
         <v>9088000</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>20018</v>
+        <v>19974</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
@@ -28394,7 +28386,7 @@
         <v>9088000</v>
       </c>
       <c r="L426" s="5" t="n">
-        <v>20018</v>
+        <v>19974</v>
       </c>
       <c r="M426" s="3" t="inlineStr">
         <is>
@@ -28693,7 +28685,7 @@
         </is>
       </c>
       <c r="E431" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
@@ -28709,7 +28701,7 @@
         <v>4425000</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>17700</v>
+        <v>17771</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
@@ -28720,7 +28712,7 @@
         <v>4425000</v>
       </c>
       <c r="L431" s="5" t="n">
-        <v>17700</v>
+        <v>17771</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
@@ -28755,7 +28747,7 @@
         </is>
       </c>
       <c r="E432" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
@@ -28771,7 +28763,7 @@
         <v>5587000</v>
       </c>
       <c r="I432" s="5" t="n">
-        <v>17459</v>
+        <v>17514</v>
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
@@ -28782,7 +28774,7 @@
         <v>5587000</v>
       </c>
       <c r="L432" s="5" t="n">
-        <v>17459</v>
+        <v>17514</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
@@ -28817,7 +28809,7 @@
         </is>
       </c>
       <c r="E433" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
@@ -28833,7 +28825,7 @@
         <v>5559000</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>17372</v>
+        <v>17426</v>
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
@@ -28844,7 +28836,7 @@
         <v>5559000</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>17372</v>
+        <v>17426</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
@@ -28910,7 +28902,7 @@
       </c>
       <c r="M434" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N434" s="3" t="inlineStr">
@@ -28941,7 +28933,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -28957,7 +28949,7 @@
         <v>6064000</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>18432</v>
+        <v>18376</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -28968,7 +28960,7 @@
         <v>6064000</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>18432</v>
+        <v>18376</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -29003,7 +28995,7 @@
         </is>
       </c>
       <c r="E436" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
@@ -29019,7 +29011,7 @@
         <v>9065000</v>
       </c>
       <c r="I436" s="5" t="n">
-        <v>19967</v>
+        <v>19923</v>
       </c>
       <c r="J436" s="3" t="inlineStr">
         <is>
@@ -29030,7 +29022,7 @@
         <v>9065000</v>
       </c>
       <c r="L436" s="5" t="n">
-        <v>19967</v>
+        <v>19923</v>
       </c>
       <c r="M436" s="3" t="inlineStr">
         <is>
@@ -29329,7 +29321,7 @@
         </is>
       </c>
       <c r="E441" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
@@ -29345,7 +29337,7 @@
         <v>4222000</v>
       </c>
       <c r="I441" s="5" t="n">
-        <v>16888</v>
+        <v>16956</v>
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
@@ -29356,7 +29348,7 @@
         <v>4222000</v>
       </c>
       <c r="L441" s="5" t="n">
-        <v>16888</v>
+        <v>16956</v>
       </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
@@ -29391,7 +29383,7 @@
         </is>
       </c>
       <c r="E442" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
@@ -29407,7 +29399,7 @@
         <v>5574000</v>
       </c>
       <c r="I442" s="5" t="n">
-        <v>17419</v>
+        <v>17473</v>
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
@@ -29418,7 +29410,7 @@
         <v>5574000</v>
       </c>
       <c r="L442" s="5" t="n">
-        <v>17419</v>
+        <v>17473</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
@@ -29453,7 +29445,7 @@
         </is>
       </c>
       <c r="E443" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F443" s="3" t="inlineStr">
         <is>
@@ -29469,7 +29461,7 @@
         <v>5545000</v>
       </c>
       <c r="I443" s="5" t="n">
-        <v>17328</v>
+        <v>17382</v>
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
@@ -29480,7 +29472,7 @@
         <v>5545000</v>
       </c>
       <c r="L443" s="5" t="n">
-        <v>17328</v>
+        <v>17382</v>
       </c>
       <c r="M443" s="3" t="inlineStr">
         <is>
@@ -29546,7 +29538,7 @@
       </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N444" s="3" t="inlineStr">
@@ -29577,7 +29569,7 @@
         </is>
       </c>
       <c r="E445" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
@@ -29593,7 +29585,7 @@
         <v>5981000</v>
       </c>
       <c r="I445" s="5" t="n">
-        <v>18179</v>
+        <v>18124</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
@@ -29604,7 +29596,7 @@
         <v>5981000</v>
       </c>
       <c r="L445" s="5" t="n">
-        <v>18179</v>
+        <v>18124</v>
       </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
@@ -29639,7 +29631,7 @@
         </is>
       </c>
       <c r="E446" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
@@ -29655,7 +29647,7 @@
         <v>9043000</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>19919</v>
+        <v>19875</v>
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
@@ -29666,7 +29658,7 @@
         <v>9043000</v>
       </c>
       <c r="L446" s="5" t="n">
-        <v>19919</v>
+        <v>19875</v>
       </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
@@ -29965,7 +29957,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
@@ -29981,7 +29973,7 @@
         <v>4211000</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>16844</v>
+        <v>16912</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -29992,7 +29984,7 @@
         <v>4211000</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>16844</v>
+        <v>16912</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
@@ -30027,7 +30019,7 @@
         </is>
       </c>
       <c r="E452" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
@@ -30043,7 +30035,7 @@
         <v>5559000</v>
       </c>
       <c r="I452" s="5" t="n">
-        <v>17372</v>
+        <v>17426</v>
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
@@ -30054,7 +30046,7 @@
         <v>5559000</v>
       </c>
       <c r="L452" s="5" t="n">
-        <v>17372</v>
+        <v>17426</v>
       </c>
       <c r="M452" s="3" t="inlineStr">
         <is>
@@ -30089,7 +30081,7 @@
         </is>
       </c>
       <c r="E453" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
@@ -30105,7 +30097,7 @@
         <v>5531000</v>
       </c>
       <c r="I453" s="5" t="n">
-        <v>17284</v>
+        <v>17339</v>
       </c>
       <c r="J453" s="3" t="inlineStr">
         <is>
@@ -30116,7 +30108,7 @@
         <v>5531000</v>
       </c>
       <c r="L453" s="5" t="n">
-        <v>17284</v>
+        <v>17339</v>
       </c>
       <c r="M453" s="3" t="inlineStr">
         <is>
@@ -30213,7 +30205,7 @@
         </is>
       </c>
       <c r="E455" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
@@ -30229,7 +30221,7 @@
         <v>5966000</v>
       </c>
       <c r="I455" s="5" t="n">
-        <v>18134</v>
+        <v>18079</v>
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
@@ -30240,7 +30232,7 @@
         <v>5966000</v>
       </c>
       <c r="L455" s="5" t="n">
-        <v>18134</v>
+        <v>18079</v>
       </c>
       <c r="M455" s="3" t="inlineStr">
         <is>
@@ -30275,7 +30267,7 @@
         </is>
       </c>
       <c r="E456" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
@@ -30291,7 +30283,7 @@
         <v>9020000</v>
       </c>
       <c r="I456" s="5" t="n">
-        <v>19868</v>
+        <v>19824</v>
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
@@ -30302,7 +30294,7 @@
         <v>9020000</v>
       </c>
       <c r="L456" s="5" t="n">
-        <v>19868</v>
+        <v>19824</v>
       </c>
       <c r="M456" s="3" t="inlineStr">
         <is>
@@ -30601,7 +30593,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
@@ -30617,7 +30609,7 @@
         <v>4201000</v>
       </c>
       <c r="I461" s="5" t="n">
-        <v>16804</v>
+        <v>16871</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
@@ -30628,7 +30620,7 @@
         <v>4201000</v>
       </c>
       <c r="L461" s="5" t="n">
-        <v>16804</v>
+        <v>16871</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
@@ -30663,7 +30655,7 @@
         </is>
       </c>
       <c r="E462" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
@@ -30679,7 +30671,7 @@
         <v>5608000</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>17525</v>
+        <v>17580</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
@@ -30690,7 +30682,7 @@
         <v>5608000</v>
       </c>
       <c r="L462" s="5" t="n">
-        <v>17525</v>
+        <v>17580</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
@@ -30725,7 +30717,7 @@
         </is>
       </c>
       <c r="E463" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
@@ -30741,7 +30733,7 @@
         <v>5769000</v>
       </c>
       <c r="I463" s="5" t="n">
-        <v>18028</v>
+        <v>18085</v>
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
@@ -30752,7 +30744,7 @@
         <v>5769000</v>
       </c>
       <c r="L463" s="5" t="n">
-        <v>18028</v>
+        <v>18085</v>
       </c>
       <c r="M463" s="3" t="inlineStr">
         <is>
@@ -30818,7 +30810,7 @@
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N464" s="3" t="inlineStr">
@@ -30849,7 +30841,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -30865,7 +30857,7 @@
         <v>5952000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>18091</v>
+        <v>18036</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -30876,7 +30868,7 @@
         <v>5952000</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>18091</v>
+        <v>18036</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -30911,7 +30903,7 @@
         </is>
       </c>
       <c r="E466" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
@@ -30927,7 +30919,7 @@
         <v>8998000</v>
       </c>
       <c r="I466" s="5" t="n">
-        <v>19819</v>
+        <v>19776</v>
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
@@ -30938,7 +30930,7 @@
         <v>8998000</v>
       </c>
       <c r="L466" s="5" t="n">
-        <v>19819</v>
+        <v>19776</v>
       </c>
       <c r="M466" s="3" t="inlineStr">
         <is>
@@ -31237,7 +31229,7 @@
         </is>
       </c>
       <c r="E471" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
@@ -31253,7 +31245,7 @@
         <v>4191000</v>
       </c>
       <c r="I471" s="5" t="n">
-        <v>16764</v>
+        <v>16831</v>
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
@@ -31264,7 +31256,7 @@
         <v>4191000</v>
       </c>
       <c r="L471" s="5" t="n">
-        <v>16764</v>
+        <v>16831</v>
       </c>
       <c r="M471" s="3" t="inlineStr">
         <is>
@@ -31299,7 +31291,7 @@
         </is>
       </c>
       <c r="E472" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
@@ -31315,7 +31307,7 @@
         <v>5531000</v>
       </c>
       <c r="I472" s="5" t="n">
-        <v>17284</v>
+        <v>17339</v>
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
@@ -31326,7 +31318,7 @@
         <v>5531000</v>
       </c>
       <c r="L472" s="5" t="n">
-        <v>17284</v>
+        <v>17339</v>
       </c>
       <c r="M472" s="3" t="inlineStr">
         <is>
@@ -31361,7 +31353,7 @@
         </is>
       </c>
       <c r="E473" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F473" s="3" t="inlineStr">
         <is>
@@ -31377,7 +31369,7 @@
         <v>5817000</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>18178</v>
+        <v>18235</v>
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
@@ -31388,7 +31380,7 @@
         <v>5817000</v>
       </c>
       <c r="L473" s="5" t="n">
-        <v>18178</v>
+        <v>18235</v>
       </c>
       <c r="M473" s="3" t="inlineStr">
         <is>
@@ -31454,7 +31446,7 @@
       </c>
       <c r="M474" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N474" s="3" t="inlineStr">
@@ -31485,7 +31477,7 @@
         </is>
       </c>
       <c r="E475" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
@@ -31501,7 +31493,7 @@
         <v>5937000</v>
       </c>
       <c r="I475" s="5" t="n">
-        <v>18046</v>
+        <v>17991</v>
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
@@ -31512,7 +31504,7 @@
         <v>5937000</v>
       </c>
       <c r="L475" s="5" t="n">
-        <v>18046</v>
+        <v>17991</v>
       </c>
       <c r="M475" s="3" t="inlineStr">
         <is>
@@ -31547,7 +31539,7 @@
         </is>
       </c>
       <c r="E476" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
@@ -31563,7 +31555,7 @@
         <v>9078000</v>
       </c>
       <c r="I476" s="5" t="n">
-        <v>19996</v>
+        <v>19952</v>
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
@@ -31574,7 +31566,7 @@
         <v>9078000</v>
       </c>
       <c r="L476" s="5" t="n">
-        <v>19996</v>
+        <v>19952</v>
       </c>
       <c r="M476" s="3" t="inlineStr">
         <is>
@@ -31873,7 +31865,7 @@
         </is>
       </c>
       <c r="E481" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
@@ -31889,7 +31881,7 @@
         <v>4511000</v>
       </c>
       <c r="I481" s="5" t="n">
-        <v>18044</v>
+        <v>18116</v>
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
@@ -31900,7 +31892,7 @@
         <v>4511000</v>
       </c>
       <c r="L481" s="5" t="n">
-        <v>18044</v>
+        <v>18116</v>
       </c>
       <c r="M481" s="3" t="inlineStr">
         <is>
@@ -31935,7 +31927,7 @@
         </is>
       </c>
       <c r="E482" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
@@ -31951,7 +31943,7 @@
         <v>5477000</v>
       </c>
       <c r="I482" s="5" t="n">
-        <v>17116</v>
+        <v>17169</v>
       </c>
       <c r="J482" s="3" t="inlineStr">
         <is>
@@ -31962,7 +31954,7 @@
         <v>5477000</v>
       </c>
       <c r="L482" s="5" t="n">
-        <v>17116</v>
+        <v>17169</v>
       </c>
       <c r="M482" s="3" t="inlineStr">
         <is>
@@ -32090,7 +32082,7 @@
       </c>
       <c r="M484" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N484" s="3" t="inlineStr">
@@ -32121,7 +32113,7 @@
         </is>
       </c>
       <c r="E485" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
@@ -32137,7 +32129,7 @@
         <v>5957000</v>
       </c>
       <c r="I485" s="5" t="n">
-        <v>18106</v>
+        <v>18052</v>
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
@@ -32148,7 +32140,7 @@
         <v>5957000</v>
       </c>
       <c r="L485" s="5" t="n">
-        <v>18106</v>
+        <v>18052</v>
       </c>
       <c r="M485" s="3" t="inlineStr">
         <is>
@@ -32183,7 +32175,7 @@
         </is>
       </c>
       <c r="E486" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
@@ -32199,7 +32191,7 @@
         <v>9032000</v>
       </c>
       <c r="I486" s="5" t="n">
-        <v>19894</v>
+        <v>19851</v>
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
@@ -32210,7 +32202,7 @@
         <v>9032000</v>
       </c>
       <c r="L486" s="5" t="n">
-        <v>19894</v>
+        <v>19851</v>
       </c>
       <c r="M486" s="3" t="inlineStr">
         <is>
@@ -32509,7 +32501,7 @@
         </is>
       </c>
       <c r="E491" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F491" s="3" t="inlineStr">
         <is>
@@ -32525,7 +32517,7 @@
         <v>4500000</v>
       </c>
       <c r="I491" s="5" t="n">
-        <v>18000</v>
+        <v>18072</v>
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
@@ -32536,7 +32528,7 @@
         <v>4500000</v>
       </c>
       <c r="L491" s="5" t="n">
-        <v>18000</v>
+        <v>18072</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
@@ -32633,7 +32625,7 @@
         </is>
       </c>
       <c r="E493" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F493" s="3" t="inlineStr">
         <is>
@@ -32649,7 +32641,7 @@
         <v>5464000</v>
       </c>
       <c r="I493" s="5" t="n">
-        <v>17075</v>
+        <v>17129</v>
       </c>
       <c r="J493" s="3" t="inlineStr">
         <is>
@@ -32660,7 +32652,7 @@
         <v>5464000</v>
       </c>
       <c r="L493" s="5" t="n">
-        <v>17075</v>
+        <v>17129</v>
       </c>
       <c r="M493" s="3" t="inlineStr">
         <is>
@@ -32757,7 +32749,7 @@
         </is>
       </c>
       <c r="E495" s="4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
@@ -32773,7 +32765,7 @@
         <v>5942000</v>
       </c>
       <c r="I495" s="5" t="n">
-        <v>18061</v>
+        <v>18006</v>
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
@@ -32784,7 +32776,7 @@
         <v>5942000</v>
       </c>
       <c r="L495" s="5" t="n">
-        <v>18061</v>
+        <v>18006</v>
       </c>
       <c r="M495" s="3" t="inlineStr">
         <is>
@@ -32819,7 +32811,7 @@
         </is>
       </c>
       <c r="E496" s="4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
@@ -32835,7 +32827,7 @@
         <v>9189000</v>
       </c>
       <c r="I496" s="5" t="n">
-        <v>20240</v>
+        <v>20196</v>
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
@@ -32846,7 +32838,7 @@
         <v>9189000</v>
       </c>
       <c r="L496" s="5" t="n">
-        <v>20240</v>
+        <v>20196</v>
       </c>
       <c r="M496" s="3" t="inlineStr">
         <is>
@@ -33153,7 +33145,7 @@
         </is>
       </c>
       <c r="E501" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
@@ -33169,7 +33161,7 @@
         <v>4804000</v>
       </c>
       <c r="I501" s="5" t="n">
-        <v>19216</v>
+        <v>19293</v>
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
@@ -33180,7 +33172,7 @@
         <v>4804000</v>
       </c>
       <c r="L501" s="5" t="n">
-        <v>19216</v>
+        <v>19293</v>
       </c>
       <c r="M501" s="3" t="inlineStr">
         <is>
@@ -33308,7 +33300,7 @@
       </c>
       <c r="M503" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N503" s="3" t="inlineStr">
@@ -33370,7 +33362,7 @@
       </c>
       <c r="M504" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N504" s="3" t="inlineStr">
@@ -33797,7 +33789,7 @@
         </is>
       </c>
       <c r="E511" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
@@ -33813,7 +33805,7 @@
         <v>4719000</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>18876</v>
+        <v>18952</v>
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
@@ -33824,7 +33816,7 @@
         <v>4719000</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>18876</v>
+        <v>18952</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
@@ -33952,7 +33944,7 @@
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N513" s="3" t="inlineStr">
@@ -34014,7 +34006,7 @@
       </c>
       <c r="M514" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N514" s="3" t="inlineStr">
@@ -34441,7 +34433,7 @@
         </is>
       </c>
       <c r="E521" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
@@ -34457,7 +34449,7 @@
         <v>4613000</v>
       </c>
       <c r="I521" s="5" t="n">
-        <v>18452</v>
+        <v>18526</v>
       </c>
       <c r="J521" s="3" t="inlineStr">
         <is>
@@ -34468,7 +34460,7 @@
         <v>4613000</v>
       </c>
       <c r="L521" s="5" t="n">
-        <v>18452</v>
+        <v>18526</v>
       </c>
       <c r="M521" s="3" t="inlineStr">
         <is>
@@ -34596,7 +34588,7 @@
       </c>
       <c r="M523" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N523" s="3" t="inlineStr">
@@ -34658,7 +34650,7 @@
       </c>
       <c r="M524" s="3" t="inlineStr">
         <is>
-          <t>醫護專享120天現金優惠付款計劃</t>
+          <t>優先進駐90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N524" s="3" t="inlineStr">
@@ -34951,7 +34943,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -34961,7 +34953,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -35020,9 +35012,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 1378呎 (4+房)
+          <t>A | 1373呎 (4+房)
 $4668万
-$33,877/呎
+$34,000/呎
 (26年-04月-08日)</t>
         </is>
       </c>
@@ -35296,9 +35288,9 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1812万
-$26,072/呎
+$26,034/呎
 (26年-10月-09日)</t>
         </is>
       </c>
@@ -35383,9 +35375,9 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $875万
-$20,297/呎
+$20,344/呎
 (26年-10月-27日)</t>
         </is>
       </c>
@@ -35438,9 +35430,9 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $791万
-$18,346/呎
+$18,388/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -35461,9 +35453,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1631万
-$23,471/呎
+$23,437/呎
 (26年-04月-27日)</t>
         </is>
       </c>
@@ -35493,9 +35485,9 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $789万
-$18,302/呎
+$18,344/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -35508,9 +35500,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1606万
-$25,092/呎
+$25,053/呎
 (26年-10月-09日)</t>
         </is>
       </c>
@@ -35548,9 +35540,9 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $796万
-$18,459/呎
+$18,502/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -35658,9 +35650,9 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $790万
-$18,323/呎
+$18,365/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -35681,9 +35673,9 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1558万
-$22,416/呎
+$22,384/呎
 (26年-01月-30日)</t>
         </is>
       </c>
@@ -35713,9 +35705,9 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $788万
-$18,276/呎
+$18,319/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -35768,9 +35760,9 @@
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $786万
-$18,230/呎
+$18,272/呎
 (26年-05月-18日)</t>
         </is>
       </c>
@@ -35791,9 +35783,9 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1550万
-$22,304/呎
+$22,272/呎
 (26年-02月-10日)</t>
         </is>
       </c>
@@ -35823,9 +35815,9 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $792万
-$18,387/呎
+$18,430/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -35846,9 +35838,9 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1546万
-$22,249/呎
+$22,217/呎
 (26年-02月-26日)</t>
         </is>
       </c>
@@ -35878,9 +35870,9 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $782万
-$18,139/呎
+$18,181/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -35893,17 +35885,17 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1444万
-$22,564/呎
+$22,529/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1542万
-$22,193/呎
+$22,161/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -35933,9 +35925,9 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $780万
-$18,095/呎
+$18,137/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -35948,17 +35940,17 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1432万
-$22,383/呎
+$22,348/呎
 (26年-05月-06日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1556万
-$22,388/呎
+$22,356/呎
 (26年-01月-21日)</t>
         </is>
       </c>
@@ -35988,9 +35980,9 @@
       </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $769万
-$17,849/呎
+$17,891/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -36003,17 +35995,17 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1429万
-$22,327/呎
+$22,292/呎
 (26年-05月-07日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1604万
-$23,085/呎
+$23,052/呎
 (26年-01月-08日)</t>
         </is>
       </c>
@@ -36043,9 +36035,9 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $776万
-$18,005/呎
+$18,047/呎
 (26年-05月-13日)</t>
         </is>
       </c>
@@ -36058,17 +36050,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1433万
-$22,397/呎
+$22,362/呎
 (26年-05月-21日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1531万
-$22,027/呎
+$21,996/呎
 (26年-03月-04日)</t>
         </is>
       </c>
@@ -36098,9 +36090,9 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $729万
-$16,914/呎
+$16,953/呎
 (26年-01月-06日)</t>
         </is>
       </c>
@@ -36113,17 +36105,17 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1426万
-$22,284/呎
+$22,250/呎
 (26年-05月-18日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1523万
-$21,917/呎
+$21,885/呎
 (26年-02月-23日)</t>
         </is>
       </c>
@@ -36153,9 +36145,9 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $725万
-$16,828/呎
+$16,867/呎
 (26年-01月-08日)</t>
         </is>
       </c>
@@ -36168,17 +36160,17 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1415万
-$22,105/呎
+$22,070/呎
 (26年-05月-07日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1520万
-$21,863/呎
+$21,832/呎
 (26年-03月-02日)</t>
         </is>
       </c>
@@ -36208,9 +36200,9 @@
       </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $724万
-$16,789/呎
+$16,828/呎
 (26年-01月-08日)</t>
         </is>
       </c>
@@ -36223,17 +36215,17 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1357万
-$21,202/呎
+$21,168/呎
 (26年-01月-14日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1516万
-$21,809/呎
+$21,777/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -36263,9 +36255,9 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $722万
-$16,745/呎
+$16,784/呎
 (26年-01月-06日)</t>
         </is>
       </c>
@@ -36278,17 +36270,17 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1416万
-$22,119/呎
+$22,084/呎
 (26年-05月-21日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1512万
-$21,754/呎
+$21,723/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -36318,9 +36310,9 @@
       </c>
       <c r="G28" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $720万
-$16,705/呎
+$16,744/呎
 (26年-01月-07日)</t>
         </is>
       </c>
@@ -36333,17 +36325,17 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1404万
-$21,941/呎
+$21,906/呎
 (26年-05月-08日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1508万
-$21,699/呎
+$21,668/呎
 (26年-02月-25日)</t>
         </is>
       </c>
@@ -36373,9 +36365,9 @@
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $718万
-$16,661/呎
+$16,700/呎
 (26年-01月-02日)</t>
         </is>
       </c>
@@ -36388,17 +36380,17 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1401万
-$21,884/呎
+$21,850/呎
 (26年-05月-13日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1522万
-$21,892/呎
+$21,861/呎
 (26年-02月-26日)</t>
         </is>
       </c>
@@ -36428,9 +36420,9 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $716万
-$16,622/呎
+$16,660/呎
 (26年-01月-07日)</t>
         </is>
       </c>
@@ -36443,17 +36435,17 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1397万
-$21,831/呎
+$21,797/呎
 (26年-05月-06日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1501万
-$21,591/呎
+$21,560/呎
 (26年-01月-14日)</t>
         </is>
       </c>
@@ -36483,9 +36475,9 @@
       </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $750万
-$17,408/呎
+$17,449/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -36498,17 +36490,17 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 640呎 (3房)
+          <t>A | 641呎 (3房)
 $1340万
-$20,939/呎
+$20,906/呎
 (26年-01月-15日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1497万
-$21,538/呎
+$21,507/呎
 (26年-01月-16日)</t>
         </is>
       </c>
@@ -36538,9 +36530,9 @@
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $748万
-$17,367/呎
+$17,407/呎
 (26年-05月-14日)</t>
         </is>
       </c>
@@ -36561,9 +36553,9 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>B | 695呎 (3房)
+          <t>B | 696呎 (3房)
 $1557万
-$22,404/呎
+$22,372/呎
 (26年-04月-22日)</t>
         </is>
       </c>
@@ -36593,9 +36585,9 @@
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $753万
-$17,473/呎
+$17,514/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -36619,7 +36611,7 @@
           <t>B | 696呎 (3房)
 $1694万
 $24,333/呎
-(26年-10月-05日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -36648,9 +36640,9 @@
       </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
-          <t>F | 431呎 (2房)
+          <t>F | 430呎 (2房)
 $743万
-$17,234/呎
+$17,274/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -36669,12 +36661,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 696呎 (3房)
-招标单位
--
-(在售)</t>
+$1689万
+$24,273/呎
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -36891,12 +36883,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -37111,7 +37103,7 @@
           <t>G | 249呎 (开放式)
 $522万
 $20,948/呎
-(26年-10月-06日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">
@@ -37198,7 +37190,7 @@
           <t>G | 249呎 (开放式)
 $519万
 $20,843/呎
-(26年-10月-03日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="I7" s="24" t="inlineStr">
@@ -37250,9 +37242,9 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $639万
-$19,416/呎
+$19,358/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -37266,25 +37258,25 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $622万
-$19,431/呎
+$19,492/呎
 (26年-05月-15日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $620万
-$19,369/呎
+$19,429/呎
 (26年-05月-06日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $478万
-$19,136/呎
+$19,213/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -37337,9 +37329,9 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $637万
-$19,368/呎
+$19,309/呎
 (26年-05月-21日)</t>
         </is>
       </c>
@@ -37353,25 +37345,25 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $620万
-$19,384/呎
+$19,445/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $618万
-$19,319/呎
+$19,379/呎
 (26年-05月-07日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $477万
-$19,092/呎
+$19,169/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -37424,9 +37416,9 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $643万
-$19,535/呎
+$19,476/呎
 (26年-05月-21日)</t>
         </is>
       </c>
@@ -37440,25 +37432,25 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $619万
-$19,338/呎
+$19,398/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $622万
-$19,431/呎
+$19,492/呎
 (26年-05月-15日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $482万
-$19,260/呎
+$19,337/呎
 (26年-05月-20日)</t>
         </is>
       </c>
@@ -37511,9 +37503,9 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $629万
-$19,109/呎
+$19,052/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -37527,25 +37519,25 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $617万
-$19,291/呎
+$19,351/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $622万
-$19,438/呎
+$19,498/呎
 (26年-04月-10日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $475万
-$18,996/呎
+$19,072/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -37598,9 +37590,9 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $627万
-$19,061/呎
+$19,003/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -37614,34 +37606,34 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $616万
-$19,241/呎
+$19,301/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $614万
-$19,175/呎
+$19,235/呎
 (26年-05月-06日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $474万
-$18,948/呎
+$19,024/呎
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $761万
 $23,630/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -37685,9 +37677,9 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $626万
-$19,015/呎
+$18,958/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -37701,25 +37693,25 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $613万
-$19,156/呎
+$19,216/呎
 (26年-04月-29日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $583万
-$18,219/呎
+$18,276/呎
 (26年-03月-02日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $473万
-$18,904/呎
+$18,980/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -37728,7 +37720,7 @@
           <t>H | 322呎 (1房)
 $676万
 $20,981/呎
-(26年-10月-02日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -37764,17 +37756,17 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $962万
-$21,198/呎
+$21,152/呎
 (26年-05月-07日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $624万
-$18,967/呎
+$18,909/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -37788,25 +37780,25 @@
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $611万
-$19,106/呎
+$19,166/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $582万
-$18,172/呎
+$18,229/呎
 (26年-02月-23日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $471万
-$18,852/呎
+$18,928/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -37938,17 +37930,17 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $955万
-$21,040/呎
+$20,993/呎
 (26年-05月-08日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $619万
-$18,827/呎
+$18,770/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -37962,34 +37954,34 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $607万
-$18,966/呎
+$19,025/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $577万
-$18,038/呎
+$18,094/呎
 (26年-02月-26日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $468万
-$18,712/呎
+$18,787/呎
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $751万
 $23,335/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -38025,17 +38017,17 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $953万
-$20,987/呎
+$20,941/呎
 (26年-05月-13日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $618万
-$18,781/呎
+$18,724/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38049,34 +38041,34 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $579万
-$18,106/呎
+$18,163/呎
 (26年-02月-24日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $576万
-$17,991/呎
+$18,047/呎
 (26年-02月-25日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $467万
-$18,668/呎
+$18,743/呎
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $750万
 $23,280/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -38112,17 +38104,17 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $961万
-$21,172/呎
+$21,125/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $616万
-$18,733/呎
+$18,676/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38136,25 +38128,25 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $604万
-$18,872/呎
+$18,931/呎
 (26年-04月-29日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $574万
-$17,944/呎
+$18,000/呎
 (26年-02月-13日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $471万
-$18,828/呎
+$18,904/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -38199,17 +38191,17 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $959万
-$21,117/呎
+$21,070/呎
 (26年-05月-18日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $615万
-$18,687/呎
+$18,630/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38223,25 +38215,25 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $602万
-$18,825/呎
+$18,884/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $573万
-$17,900/呎
+$17,956/呎
 (26年-02月-05日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $475万
-$18,992/呎
+$19,068/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -38286,17 +38278,17 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $946万
-$20,830/呎
+$20,785/呎
 (26年-05月-08日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $613万
-$18,641/呎
+$18,585/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38310,34 +38302,34 @@
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $601万
-$18,775/呎
+$18,834/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $571万
-$17,856/呎
+$17,912/呎
 (26年-02月-02日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $468万
-$18,736/呎
+$18,811/呎
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $744万
 $23,106/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -38373,17 +38365,17 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $943万
-$20,780/呎
+$20,734/呎
 (26年-05月-08日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $612万
-$18,593/呎
+$18,536/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38397,25 +38389,25 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $599万
-$18,728/呎
+$18,787/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $570万
-$17,812/呎
+$17,868/呎
 (26年-01月-23日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $462万
-$18,480/呎
+$18,554/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -38460,17 +38452,17 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $923万
-$20,322/呎
+$20,277/呎
 (26年-03月-03日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $610万
-$18,547/呎
+$18,491/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38484,25 +38476,25 @@
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $566万
-$17,678/呎
+$17,734/呎
 (26年-02月-13日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $568万
-$17,766/呎
+$17,821/呎
 (26年-02月-04日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $461万
-$18,436/呎
+$18,510/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -38547,17 +38539,17 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $931万
-$20,500/呎
+$20,455/呎
 (26年-03月-05日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $609万
-$18,498/呎
+$18,442/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38571,25 +38563,25 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $564万
-$17,634/呎
+$17,690/呎
 (26年-01月-08日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $567万
-$17,722/呎
+$17,777/呎
 (26年-02月-06日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $465万
-$18,596/呎
+$18,671/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38634,17 +38626,17 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $918万
-$20,220/呎
+$20,176/呎
 (26年-02月-26日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $607万
-$18,453/呎
+$18,397/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -38658,34 +38650,34 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $563万
-$17,591/呎
+$17,646/呎
 (26年-01月-13日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $566万
-$17,678/呎
+$17,734/呎
 (26年-02月-06日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $459万
-$18,344/呎
+$18,418/呎
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>H | 322呎 (1房)
 $737万
 $22,876/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -38721,17 +38713,17 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $913万
-$20,119/呎
+$20,075/呎
 (26年-03月-02日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $604万
-$18,362/呎
+$18,306/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38745,25 +38737,25 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $560万
-$17,503/呎
+$17,558/呎
 (26年-01月-09日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $563万
-$17,591/呎
+$17,646/呎
 (26年-02月-16日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $426万
-$17,056/呎
+$17,124/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -38808,17 +38800,17 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $911万
-$20,068/呎
+$20,024/呎
 (26年-02月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $603万
-$18,319/呎
+$18,264/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38832,25 +38824,25 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $559万
-$17,462/呎
+$17,517/呎
 (26年-01月-09日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $562万
-$17,547/呎
+$17,602/呎
 (26年-02月-06日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $425万
-$17,016/呎
+$17,084/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -38895,17 +38887,17 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $909万
-$20,018/呎
+$19,974/呎
 (26年-02月-05日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $601万
-$18,274/呎
+$18,218/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -38919,25 +38911,25 @@
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $557万
-$17,419/呎
+$17,473/呎
 (26年-01月-09日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $560万
-$17,503/呎
+$17,558/呎
 (26年-01月-26日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $424万
-$16,972/呎
+$17,040/呎
 (26年-01月-14日)</t>
         </is>
       </c>
@@ -38982,17 +38974,17 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $906万
-$19,967/呎
+$19,923/呎
 (26年-03月-02日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $606万
-$18,432/呎
+$18,376/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -39006,25 +38998,25 @@
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $556万
-$17,372/呎
+$17,426/呎
 (26年-01月-12日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $559万
-$17,459/呎
+$17,514/呎
 (26年-02月-13日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $442万
-$17,700/呎
+$17,771/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -39069,17 +39061,17 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $904万
-$19,919/呎
+$19,875/呎
 (26年-03月-02日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $598万
-$18,179/呎
+$18,124/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -39093,25 +39085,25 @@
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $554万
-$17,328/呎
+$17,382/呎
 (26年-01月-09日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $557万
-$17,419/呎
+$17,473/呎
 (26年-02月-13日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $422万
-$16,888/呎
+$16,956/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -39156,17 +39148,17 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $902万
-$19,868/呎
+$19,824/呎
 (26年-01月-14日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $597万
-$18,134/呎
+$18,079/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -39180,25 +39172,25 @@
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $553万
-$17,284/呎
+$17,339/呎
 (26年-01月-19日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $556万
-$17,372/呎
+$17,426/呎
 (26年-02月-24日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $421万
-$16,844/呎
+$16,912/呎
 (26年-01月-08日)</t>
         </is>
       </c>
@@ -39243,17 +39235,17 @@
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $900万
-$19,819/呎
+$19,776/呎
 (26年-02月-26日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $595万
-$18,091/呎
+$18,036/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -39267,25 +39259,25 @@
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $577万
-$18,028/呎
+$18,085/呎
 (26年-01月-13日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $561万
-$17,525/呎
+$17,580/呎
 (26年-01月-26日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $420万
-$16,804/呎
+$16,871/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -39330,17 +39322,17 @@
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $908万
-$19,996/呎
+$19,952/呎
 (26年-03月-16日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $594万
-$18,046/呎
+$17,991/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -39354,25 +39346,25 @@
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $582万
-$18,178/呎
+$18,235/呎
 (26年-04月-23日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $553万
-$17,284/呎
+$17,339/呎
 (26年-02月-11日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $419万
-$16,764/呎
+$16,831/呎
 (26年-01月-14日)</t>
         </is>
       </c>
@@ -39417,17 +39409,17 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $903万
-$19,894/呎
+$19,851/呎
 (26年-03月-17日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $596万
-$18,106/呎
+$18,052/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -39449,17 +39441,17 @@
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>F | 320呎 (1房)
+          <t>F | 319呎 (1房)
 $548万
-$17,116/呎
+$17,169/呎
 (26年-02月-25日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $451万
-$18,044/呎
+$18,116/呎
 (26年-05月-15日)</t>
         </is>
       </c>
@@ -39504,17 +39496,17 @@
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>B | 454呎 (2房)
+          <t>B | 455呎 (2房)
 $919万
-$20,240/呎
+$20,196/呎
 (26年-05月-18日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>C | 329呎 (1房)
+          <t>C | 330呎 (1房)
 $594万
-$18,061/呎
+$18,006/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -39528,9 +39520,9 @@
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>E | 320呎 (1房)
+          <t>E | 319呎 (1房)
 $546万
-$17,075/呎
+$17,129/呎
 (26年-01月-15日)</t>
         </is>
       </c>
@@ -39544,9 +39536,9 @@
       </c>
       <c r="H34" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $450万
-$18,000/呎
+$18,072/呎
 (26年-05月-18日)</t>
         </is>
       </c>
@@ -39631,9 +39623,9 @@
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $480万
-$19,216/呎
+$19,293/呎
 (26年-10月-13日)</t>
         </is>
       </c>
@@ -39718,9 +39710,9 @@
       </c>
       <c r="H36" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $472万
-$18,876/呎
+$18,952/呎
 (26年-10月-16日)</t>
         </is>
       </c>
@@ -39805,9 +39797,9 @@
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>G | 250呎 (开放式)
+          <t>G | 249呎 (开放式)
 $461万
-$18,452/呎
+$18,526/呎
 (26年-10月-09日)</t>
         </is>
       </c>
